--- a/source/bin/excel/character.xlsx
+++ b/source/bin/excel/character.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\liqi-excel\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Git\liqi-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{549333E8-EA90-4822-9B6E-95F43F3CC1F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D7686A9-8E0F-47D3-B601-EEEEAD970E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="885" yWindow="-120" windowWidth="28035" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="export" sheetId="4" r:id="rId1"/>
@@ -125,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6918" uniqueCount="687">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6969" uniqueCount="702">
   <si>
     <t>sheet</t>
   </si>
@@ -2726,12 +2726,67 @@
     <t>yuanxiao_25wuxia_eff3</t>
     <phoneticPr fontId="16" type="noConversion"/>
   </si>
+  <si>
+    <t>辉夜姬约会</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>岚星约会</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>HYJ_SE_402907/celebrate</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>HYJ_SE_402907/greeting</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>HYJ_SE_402907/click</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>LX_SE_407404/celebrate</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>LX_SE_407404/greeting</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>LX_SE_407404/click</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>lanxing_25yh_eff2</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>lanxing_25yh_eff3</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>摇曳心情</t>
+  </si>
+  <si>
+    <t>搖曳心情</t>
+  </si>
+  <si>
+    <t>高鳴るハート</t>
+  </si>
+  <si>
+    <t>Idle Hours</t>
+  </si>
+  <si>
+    <t>설레는 마음</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="37" x14ac:knownFonts="1">
+  <fonts count="38" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3001,6 +3056,14 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -3108,7 +3171,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3224,6 +3287,9 @@
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3598,7 +3664,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:U834"/>
+  <dimension ref="A1:U838"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
@@ -3775,14 +3841,14 @@
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>48</v>
+      </c>
       <c r="D4"/>
       <c r="E4"/>
       <c r="F4"/>
       <c r="G4"/>
       <c r="H4"/>
-      <c r="I4" t="s">
-        <v>48</v>
-      </c>
       <c r="J4" t="s">
         <v>49</v>
       </c>
@@ -39723,7 +39789,7 @@
         <v>40011403</v>
       </c>
     </row>
-    <row r="833" spans="2:18" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="833" spans="1:18" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B833" s="28">
         <v>20000115</v>
       </c>
@@ -39770,7 +39836,7 @@
         <v>40011503</v>
       </c>
     </row>
-    <row r="834" spans="2:18" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="834" spans="1:18" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B834" s="28">
         <v>20000116</v>
       </c>
@@ -39815,6 +39881,197 @@
       </c>
       <c r="R834">
         <v>40011603</v>
+      </c>
+    </row>
+    <row r="835" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A835" s="3" t="s">
+        <v>679</v>
+      </c>
+      <c r="B835" s="28">
+        <v>200029</v>
+      </c>
+      <c r="C835">
+        <v>933</v>
+      </c>
+      <c r="D835" t="s">
+        <v>102</v>
+      </c>
+      <c r="E835" t="s">
+        <v>103</v>
+      </c>
+      <c r="F835" t="s">
+        <v>104</v>
+      </c>
+      <c r="G835" t="s">
+        <v>105</v>
+      </c>
+      <c r="H835" t="s">
+        <v>106</v>
+      </c>
+      <c r="I835">
+        <v>1</v>
+      </c>
+      <c r="L835" s="25" t="s">
+        <v>697</v>
+      </c>
+      <c r="M835" s="37" t="s">
+        <v>698</v>
+      </c>
+      <c r="N835" s="48" t="s">
+        <v>699</v>
+      </c>
+      <c r="O835" s="48" t="s">
+        <v>700</v>
+      </c>
+      <c r="P835" s="48" t="s">
+        <v>701</v>
+      </c>
+      <c r="Q835">
+        <v>3</v>
+      </c>
+      <c r="R835">
+        <v>402907</v>
+      </c>
+    </row>
+    <row r="836" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="B836" s="28">
+        <v>200074</v>
+      </c>
+      <c r="C836">
+        <v>933</v>
+      </c>
+      <c r="D836" t="s">
+        <v>102</v>
+      </c>
+      <c r="E836" t="s">
+        <v>103</v>
+      </c>
+      <c r="F836" t="s">
+        <v>104</v>
+      </c>
+      <c r="G836" t="s">
+        <v>105</v>
+      </c>
+      <c r="H836" t="s">
+        <v>106</v>
+      </c>
+      <c r="I836">
+        <v>1</v>
+      </c>
+      <c r="L836" s="25" t="s">
+        <v>697</v>
+      </c>
+      <c r="M836" s="37" t="s">
+        <v>698</v>
+      </c>
+      <c r="N836" s="48" t="s">
+        <v>699</v>
+      </c>
+      <c r="O836" s="48" t="s">
+        <v>700</v>
+      </c>
+      <c r="P836" s="48" t="s">
+        <v>701</v>
+      </c>
+      <c r="Q836">
+        <v>3</v>
+      </c>
+      <c r="R836">
+        <v>407404</v>
+      </c>
+    </row>
+    <row r="837" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="B837" s="28">
+        <v>200091</v>
+      </c>
+      <c r="C837">
+        <v>933</v>
+      </c>
+      <c r="D837" t="s">
+        <v>102</v>
+      </c>
+      <c r="E837" t="s">
+        <v>103</v>
+      </c>
+      <c r="F837" t="s">
+        <v>104</v>
+      </c>
+      <c r="G837" t="s">
+        <v>105</v>
+      </c>
+      <c r="H837" t="s">
+        <v>106</v>
+      </c>
+      <c r="I837">
+        <v>1</v>
+      </c>
+      <c r="L837" s="25" t="s">
+        <v>697</v>
+      </c>
+      <c r="M837" s="37" t="s">
+        <v>698</v>
+      </c>
+      <c r="N837" s="48" t="s">
+        <v>699</v>
+      </c>
+      <c r="O837" s="48" t="s">
+        <v>700</v>
+      </c>
+      <c r="P837" s="48" t="s">
+        <v>701</v>
+      </c>
+      <c r="Q837">
+        <v>3</v>
+      </c>
+      <c r="R837">
+        <v>409103</v>
+      </c>
+    </row>
+    <row r="838" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="B838" s="28">
+        <v>200049</v>
+      </c>
+      <c r="C838">
+        <v>933</v>
+      </c>
+      <c r="D838" t="s">
+        <v>102</v>
+      </c>
+      <c r="E838" t="s">
+        <v>103</v>
+      </c>
+      <c r="F838" t="s">
+        <v>104</v>
+      </c>
+      <c r="G838" t="s">
+        <v>105</v>
+      </c>
+      <c r="H838" t="s">
+        <v>106</v>
+      </c>
+      <c r="I838">
+        <v>1</v>
+      </c>
+      <c r="L838" s="25" t="s">
+        <v>697</v>
+      </c>
+      <c r="M838" s="37" t="s">
+        <v>698</v>
+      </c>
+      <c r="N838" s="48" t="s">
+        <v>699</v>
+      </c>
+      <c r="O838" s="48" t="s">
+        <v>700</v>
+      </c>
+      <c r="P838" s="48" t="s">
+        <v>701</v>
+      </c>
+      <c r="Q838">
+        <v>3</v>
+      </c>
+      <c r="R838">
+        <v>404905</v>
       </c>
     </row>
   </sheetData>
@@ -40208,7 +40465,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:U35"/>
+  <dimension ref="A1:U37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" customWidth="1"/>
@@ -41148,6 +41405,52 @@
       </c>
       <c r="L35" s="3" t="s">
         <v>662</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A36" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="B36">
+        <v>402907</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A37" s="3" t="s">
+        <v>688</v>
+      </c>
+      <c r="B37">
+        <v>407404</v>
+      </c>
+      <c r="C37">
+        <v>2</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>695</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>693</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>694</v>
       </c>
     </row>
   </sheetData>

--- a/source/bin/excel/character.xlsx
+++ b/source/bin/excel/character.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\liqi\liqi-excel\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\liqi-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1FDC84A-7CC4-4C46-B707-D79C25054D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{339F411B-B66C-45C7-93B9-99AE34607105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="export" sheetId="4" r:id="rId1"/>
@@ -20,6 +20,17 @@
     <sheet name="解锁类型描述" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -114,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7073" uniqueCount="717">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7125" uniqueCount="753">
   <si>
     <t>sheet</t>
   </si>
@@ -1700,14 +1711,6 @@
   </si>
   <si>
     <t>不寐之絆</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>,lingzi_24ws_01_eff</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>,lingzi_24ws_02_eff</t>
     <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
@@ -2811,10 +2814,6 @@
     <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
-    <t>tbd</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
     <t>xiangyuanwu_yd_eff3</t>
     <phoneticPr fontId="16" type="noConversion"/>
   </si>
@@ -2829,6 +2828,152 @@
   </si>
   <si>
     <t>xiangyuanwu_wq_eff3</t>
+  </si>
+  <si>
+    <t>senchuanlingzi_ws_eff1</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>senchuanlingzi_ws_eff2</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>雪间春信</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>雪間春信</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>雪間の春兆</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>Snowkissed Tidings</t>
+  </si>
+  <si>
+    <t>흰 눈 사이의 봄편지</t>
+  </si>
+  <si>
+    <t>纯白乐章</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>純白樂章</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>ユキノソナタ</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>Song of the Bells</t>
+  </si>
+  <si>
+    <t>순백의 악장</t>
+  </si>
+  <si>
+    <t>26lfx3</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>流连深蓝</t>
+  </si>
+  <si>
+    <t>流連深藍</t>
+  </si>
+  <si>
+    <t>青に夢中</t>
+  </si>
+  <si>
+    <t>Susurrus of Blue</t>
+  </si>
+  <si>
+    <t>끝없는 푸름</t>
+  </si>
+  <si>
+    <t>花语白礼服</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>huayubai_26lf_eff2</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>HYB_SE_409903/celebrate</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>HYB_SE_409903/greeting</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>HYB_SE_409903/click</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>花语青礼服</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>HYQ_SE_409803/celebrate</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>HYQ_SE_409803/greeting</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>HYQ_SE_409803/click</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>福姬春节</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>伊芙春节</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>局春节</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>fj_se_403807/celebrate</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>fj_se_403807/greeting</t>
+  </si>
+  <si>
+    <t>fj_se_403807/click</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>yf_se_408304/celebrate</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>yf_se_408304/greeting</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>yf_se_408304/click</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>j_se_409203/celebrate</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>j_se_409203/greeting</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>j_se_409203/click</t>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3220,7 +3365,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3339,6 +3484,9 @@
     </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3713,7 +3861,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:U850"/>
+  <dimension ref="A1:U853"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
@@ -16223,7 +16371,7 @@
     </row>
     <row r="361" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A361" s="23" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B361">
         <v>200001</v>
@@ -16256,19 +16404,19 @@
         <v>241</v>
       </c>
       <c r="L361" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M361" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N361" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M361" s="17" t="s">
+      <c r="O361" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N361" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O361" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P361" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q361">
         <v>2</v>
@@ -16312,19 +16460,19 @@
         <v>241</v>
       </c>
       <c r="L362" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M362" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N362" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M362" s="17" t="s">
+      <c r="O362" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N362" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O362" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P362" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q362">
         <v>2</v>
@@ -16368,19 +16516,19 @@
         <v>241</v>
       </c>
       <c r="L363" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M363" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N363" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M363" s="17" t="s">
+      <c r="O363" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N363" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O363" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P363" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q363">
         <v>2</v>
@@ -16424,19 +16572,19 @@
         <v>241</v>
       </c>
       <c r="L364" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M364" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N364" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M364" s="17" t="s">
+      <c r="O364" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N364" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O364" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P364" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q364">
         <v>2</v>
@@ -16480,19 +16628,19 @@
         <v>241</v>
       </c>
       <c r="L365" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M365" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N365" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M365" s="17" t="s">
+      <c r="O365" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N365" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O365" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P365" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q365">
         <v>2</v>
@@ -16536,19 +16684,19 @@
         <v>241</v>
       </c>
       <c r="L366" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M366" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N366" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M366" s="17" t="s">
+      <c r="O366" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N366" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O366" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P366" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q366">
         <v>2</v>
@@ -16592,19 +16740,19 @@
         <v>241</v>
       </c>
       <c r="L367" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M367" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N367" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M367" s="17" t="s">
+      <c r="O367" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N367" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O367" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P367" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q367">
         <v>2</v>
@@ -16648,19 +16796,19 @@
         <v>241</v>
       </c>
       <c r="L368" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M368" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N368" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M368" s="17" t="s">
+      <c r="O368" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N368" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O368" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P368" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q368">
         <v>2</v>
@@ -16704,19 +16852,19 @@
         <v>241</v>
       </c>
       <c r="L369" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M369" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N369" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M369" s="17" t="s">
+      <c r="O369" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N369" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O369" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P369" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q369">
         <v>2</v>
@@ -16760,19 +16908,19 @@
         <v>241</v>
       </c>
       <c r="L370" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M370" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N370" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M370" s="17" t="s">
+      <c r="O370" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N370" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O370" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P370" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q370">
         <v>2</v>
@@ -16816,19 +16964,19 @@
         <v>241</v>
       </c>
       <c r="L371" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M371" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N371" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M371" s="17" t="s">
+      <c r="O371" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N371" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O371" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P371" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q371">
         <v>2</v>
@@ -16872,19 +17020,19 @@
         <v>241</v>
       </c>
       <c r="L372" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M372" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N372" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M372" s="17" t="s">
+      <c r="O372" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N372" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O372" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P372" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q372">
         <v>2</v>
@@ -16928,19 +17076,19 @@
         <v>241</v>
       </c>
       <c r="L373" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M373" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N373" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M373" s="17" t="s">
+      <c r="O373" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N373" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O373" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P373" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q373">
         <v>2</v>
@@ -16984,19 +17132,19 @@
         <v>241</v>
       </c>
       <c r="L374" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M374" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N374" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M374" s="17" t="s">
+      <c r="O374" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N374" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O374" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P374" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q374">
         <v>2</v>
@@ -17040,19 +17188,19 @@
         <v>241</v>
       </c>
       <c r="L375" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M375" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N375" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M375" s="17" t="s">
+      <c r="O375" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N375" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O375" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P375" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q375">
         <v>2</v>
@@ -17096,19 +17244,19 @@
         <v>241</v>
       </c>
       <c r="L376" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M376" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N376" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M376" s="17" t="s">
+      <c r="O376" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N376" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O376" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P376" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q376">
         <v>2</v>
@@ -17152,19 +17300,19 @@
         <v>241</v>
       </c>
       <c r="L377" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M377" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N377" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M377" s="17" t="s">
+      <c r="O377" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N377" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O377" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P377" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q377">
         <v>2</v>
@@ -17205,19 +17353,19 @@
         <v>241</v>
       </c>
       <c r="L378" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M378" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N378" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M378" s="17" t="s">
+      <c r="O378" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N378" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O378" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P378" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q378">
         <v>2</v>
@@ -17258,19 +17406,19 @@
         <v>241</v>
       </c>
       <c r="L379" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M379" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N379" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M379" s="17" t="s">
+      <c r="O379" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N379" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O379" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P379" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q379">
         <v>2</v>
@@ -17311,19 +17459,19 @@
         <v>241</v>
       </c>
       <c r="L380" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M380" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N380" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M380" s="17" t="s">
+      <c r="O380" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N380" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O380" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P380" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q380">
         <v>2</v>
@@ -17364,19 +17512,19 @@
         <v>241</v>
       </c>
       <c r="L381" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M381" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N381" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M381" s="17" t="s">
+      <c r="O381" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N381" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O381" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P381" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q381">
         <v>2</v>
@@ -17417,19 +17565,19 @@
         <v>241</v>
       </c>
       <c r="L382" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M382" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N382" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M382" s="17" t="s">
+      <c r="O382" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N382" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O382" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P382" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q382">
         <v>2</v>
@@ -17470,19 +17618,19 @@
         <v>241</v>
       </c>
       <c r="L383" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M383" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N383" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M383" s="17" t="s">
+      <c r="O383" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N383" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O383" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P383" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q383">
         <v>2</v>
@@ -17523,19 +17671,19 @@
         <v>241</v>
       </c>
       <c r="L384" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M384" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N384" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M384" s="17" t="s">
+      <c r="O384" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N384" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O384" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P384" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q384">
         <v>2</v>
@@ -17576,19 +17724,19 @@
         <v>241</v>
       </c>
       <c r="L385" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M385" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N385" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M385" s="17" t="s">
+      <c r="O385" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N385" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O385" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P385" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q385">
         <v>2</v>
@@ -17629,19 +17777,19 @@
         <v>241</v>
       </c>
       <c r="L386" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M386" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N386" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M386" s="17" t="s">
+      <c r="O386" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N386" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O386" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P386" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q386">
         <v>2</v>
@@ -17682,19 +17830,19 @@
         <v>241</v>
       </c>
       <c r="L387" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M387" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N387" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M387" s="17" t="s">
+      <c r="O387" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N387" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O387" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P387" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q387">
         <v>2</v>
@@ -17735,19 +17883,19 @@
         <v>241</v>
       </c>
       <c r="L388" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M388" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N388" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M388" s="17" t="s">
+      <c r="O388" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N388" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O388" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P388" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q388">
         <v>2</v>
@@ -17788,19 +17936,19 @@
         <v>241</v>
       </c>
       <c r="L389" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M389" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N389" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M389" s="17" t="s">
+      <c r="O389" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N389" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O389" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P389" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q389">
         <v>2</v>
@@ -17841,19 +17989,19 @@
         <v>241</v>
       </c>
       <c r="L390" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M390" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N390" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M390" s="17" t="s">
+      <c r="O390" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N390" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O390" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P390" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q390">
         <v>2</v>
@@ -17894,19 +18042,19 @@
         <v>241</v>
       </c>
       <c r="L391" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M391" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N391" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M391" s="17" t="s">
+      <c r="O391" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N391" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O391" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P391" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q391">
         <v>2</v>
@@ -17947,19 +18095,19 @@
         <v>241</v>
       </c>
       <c r="L392" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M392" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N392" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M392" s="17" t="s">
+      <c r="O392" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N392" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O392" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P392" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q392">
         <v>2</v>
@@ -18000,19 +18148,19 @@
         <v>241</v>
       </c>
       <c r="L393" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M393" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N393" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M393" s="17" t="s">
+      <c r="O393" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N393" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O393" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P393" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q393">
         <v>2</v>
@@ -18053,19 +18201,19 @@
         <v>241</v>
       </c>
       <c r="L394" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M394" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N394" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M394" s="17" t="s">
+      <c r="O394" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N394" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O394" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P394" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q394">
         <v>2</v>
@@ -18106,19 +18254,19 @@
         <v>241</v>
       </c>
       <c r="L395" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M395" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N395" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M395" s="17" t="s">
+      <c r="O395" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N395" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O395" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P395" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q395">
         <v>2</v>
@@ -18159,19 +18307,19 @@
         <v>241</v>
       </c>
       <c r="L396" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M396" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N396" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M396" s="17" t="s">
+      <c r="O396" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N396" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O396" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P396" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q396">
         <v>2</v>
@@ -18212,19 +18360,19 @@
         <v>241</v>
       </c>
       <c r="L397" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M397" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N397" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M397" s="17" t="s">
+      <c r="O397" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N397" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O397" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P397" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q397">
         <v>2</v>
@@ -18265,19 +18413,19 @@
         <v>241</v>
       </c>
       <c r="L398" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M398" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N398" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M398" s="17" t="s">
+      <c r="O398" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N398" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O398" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P398" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q398">
         <v>2</v>
@@ -18318,19 +18466,19 @@
         <v>241</v>
       </c>
       <c r="L399" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M399" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N399" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M399" s="17" t="s">
+      <c r="O399" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N399" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O399" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P399" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q399">
         <v>2</v>
@@ -18371,19 +18519,19 @@
         <v>241</v>
       </c>
       <c r="L400" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M400" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N400" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M400" s="17" t="s">
+      <c r="O400" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N400" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O400" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P400" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q400">
         <v>2</v>
@@ -18424,19 +18572,19 @@
         <v>241</v>
       </c>
       <c r="L401" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M401" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N401" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M401" s="17" t="s">
+      <c r="O401" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N401" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O401" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P401" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q401">
         <v>2</v>
@@ -18477,19 +18625,19 @@
         <v>241</v>
       </c>
       <c r="L402" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M402" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N402" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M402" s="17" t="s">
+      <c r="O402" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N402" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O402" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P402" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q402">
         <v>2</v>
@@ -18530,19 +18678,19 @@
         <v>241</v>
       </c>
       <c r="L403" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M403" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N403" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M403" s="17" t="s">
+      <c r="O403" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N403" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O403" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P403" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q403">
         <v>2</v>
@@ -18583,19 +18731,19 @@
         <v>241</v>
       </c>
       <c r="L404" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M404" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N404" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M404" s="17" t="s">
+      <c r="O404" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N404" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O404" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P404" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q404">
         <v>2</v>
@@ -18636,19 +18784,19 @@
         <v>241</v>
       </c>
       <c r="L405" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M405" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N405" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M405" s="17" t="s">
+      <c r="O405" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N405" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O405" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P405" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q405">
         <v>2</v>
@@ -18689,19 +18837,19 @@
         <v>241</v>
       </c>
       <c r="L406" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M406" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N406" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M406" s="17" t="s">
+      <c r="O406" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N406" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O406" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P406" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q406">
         <v>2</v>
@@ -18742,19 +18890,19 @@
         <v>241</v>
       </c>
       <c r="L407" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M407" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N407" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M407" s="17" t="s">
+      <c r="O407" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N407" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O407" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P407" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q407">
         <v>2</v>
@@ -18795,19 +18943,19 @@
         <v>241</v>
       </c>
       <c r="L408" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M408" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N408" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M408" s="17" t="s">
+      <c r="O408" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N408" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O408" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P408" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q408">
         <v>2</v>
@@ -18848,19 +18996,19 @@
         <v>241</v>
       </c>
       <c r="L409" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M409" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N409" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M409" s="17" t="s">
+      <c r="O409" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N409" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O409" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P409" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q409">
         <v>2</v>
@@ -18901,19 +19049,19 @@
         <v>241</v>
       </c>
       <c r="L410" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M410" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N410" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M410" s="17" t="s">
+      <c r="O410" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N410" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O410" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P410" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q410">
         <v>2</v>
@@ -18954,19 +19102,19 @@
         <v>241</v>
       </c>
       <c r="L411" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M411" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N411" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M411" s="17" t="s">
+      <c r="O411" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N411" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O411" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P411" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q411">
         <v>2</v>
@@ -19007,19 +19155,19 @@
         <v>241</v>
       </c>
       <c r="L412" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M412" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N412" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M412" s="17" t="s">
+      <c r="O412" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N412" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O412" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P412" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q412">
         <v>2</v>
@@ -19060,19 +19208,19 @@
         <v>241</v>
       </c>
       <c r="L413" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M413" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N413" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M413" s="17" t="s">
+      <c r="O413" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N413" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O413" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P413" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q413">
         <v>2</v>
@@ -19113,19 +19261,19 @@
         <v>241</v>
       </c>
       <c r="L414" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M414" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N414" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M414" s="17" t="s">
+      <c r="O414" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N414" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O414" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P414" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q414">
         <v>2</v>
@@ -19166,19 +19314,19 @@
         <v>241</v>
       </c>
       <c r="L415" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M415" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N415" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M415" s="17" t="s">
+      <c r="O415" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N415" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O415" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P415" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q415">
         <v>2</v>
@@ -19219,19 +19367,19 @@
         <v>241</v>
       </c>
       <c r="L416" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M416" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N416" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M416" s="17" t="s">
+      <c r="O416" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N416" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O416" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P416" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q416">
         <v>2</v>
@@ -19272,19 +19420,19 @@
         <v>241</v>
       </c>
       <c r="L417" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M417" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N417" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M417" s="17" t="s">
+      <c r="O417" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N417" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O417" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P417" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q417">
         <v>2</v>
@@ -19325,19 +19473,19 @@
         <v>241</v>
       </c>
       <c r="L418" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M418" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N418" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M418" s="17" t="s">
+      <c r="O418" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N418" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O418" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P418" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q418">
         <v>2</v>
@@ -19378,19 +19526,19 @@
         <v>241</v>
       </c>
       <c r="L419" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M419" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N419" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M419" s="17" t="s">
+      <c r="O419" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N419" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O419" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P419" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q419">
         <v>2</v>
@@ -19431,19 +19579,19 @@
         <v>241</v>
       </c>
       <c r="L420" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M420" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N420" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M420" s="17" t="s">
+      <c r="O420" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N420" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O420" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P420" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q420">
         <v>2</v>
@@ -19484,19 +19632,19 @@
         <v>241</v>
       </c>
       <c r="L421" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M421" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N421" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M421" s="17" t="s">
+      <c r="O421" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N421" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O421" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P421" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q421">
         <v>2</v>
@@ -19537,19 +19685,19 @@
         <v>241</v>
       </c>
       <c r="L422" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M422" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N422" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M422" s="17" t="s">
+      <c r="O422" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N422" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O422" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P422" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q422">
         <v>2</v>
@@ -19590,19 +19738,19 @@
         <v>241</v>
       </c>
       <c r="L423" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M423" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N423" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M423" s="17" t="s">
+      <c r="O423" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N423" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O423" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P423" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q423">
         <v>2</v>
@@ -19643,19 +19791,19 @@
         <v>241</v>
       </c>
       <c r="L424" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M424" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N424" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M424" s="17" t="s">
+      <c r="O424" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N424" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O424" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P424" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q424">
         <v>2</v>
@@ -19696,19 +19844,19 @@
         <v>241</v>
       </c>
       <c r="L425" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M425" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N425" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M425" s="17" t="s">
+      <c r="O425" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N425" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O425" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P425" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q425">
         <v>2</v>
@@ -19749,19 +19897,19 @@
         <v>241</v>
       </c>
       <c r="L426" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M426" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N426" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M426" s="17" t="s">
+      <c r="O426" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N426" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O426" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P426" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q426">
         <v>2</v>
@@ -19802,19 +19950,19 @@
         <v>241</v>
       </c>
       <c r="L427" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M427" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N427" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M427" s="17" t="s">
+      <c r="O427" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N427" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O427" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P427" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q427">
         <v>2</v>
@@ -19855,19 +20003,19 @@
         <v>241</v>
       </c>
       <c r="L428" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M428" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N428" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M428" s="17" t="s">
+      <c r="O428" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N428" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O428" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P428" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q428">
         <v>2</v>
@@ -19908,19 +20056,19 @@
         <v>241</v>
       </c>
       <c r="L429" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M429" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N429" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M429" s="17" t="s">
+      <c r="O429" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N429" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O429" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P429" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q429">
         <v>2</v>
@@ -19961,19 +20109,19 @@
         <v>241</v>
       </c>
       <c r="L430" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M430" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N430" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M430" s="17" t="s">
+      <c r="O430" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N430" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O430" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P430" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q430">
         <v>2</v>
@@ -20014,19 +20162,19 @@
         <v>241</v>
       </c>
       <c r="L431" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M431" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N431" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M431" s="17" t="s">
+      <c r="O431" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N431" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O431" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P431" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q431">
         <v>2</v>
@@ -20067,19 +20215,19 @@
         <v>241</v>
       </c>
       <c r="L432" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M432" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N432" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M432" s="17" t="s">
+      <c r="O432" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N432" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O432" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P432" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q432">
         <v>2</v>
@@ -20120,19 +20268,19 @@
         <v>241</v>
       </c>
       <c r="L433" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M433" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N433" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M433" s="17" t="s">
+      <c r="O433" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N433" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O433" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P433" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q433">
         <v>2</v>
@@ -20173,19 +20321,19 @@
         <v>241</v>
       </c>
       <c r="L434" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M434" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N434" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M434" s="17" t="s">
+      <c r="O434" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N434" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O434" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P434" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q434">
         <v>2</v>
@@ -20226,19 +20374,19 @@
         <v>241</v>
       </c>
       <c r="L435" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M435" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N435" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M435" s="17" t="s">
+      <c r="O435" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N435" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O435" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P435" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q435">
         <v>2</v>
@@ -20279,19 +20427,19 @@
         <v>241</v>
       </c>
       <c r="L436" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M436" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N436" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M436" s="17" t="s">
+      <c r="O436" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N436" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O436" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P436" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q436">
         <v>2</v>
@@ -20332,19 +20480,19 @@
         <v>241</v>
       </c>
       <c r="L437" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M437" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N437" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M437" s="17" t="s">
+      <c r="O437" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N437" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O437" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P437" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q437">
         <v>2</v>
@@ -20385,19 +20533,19 @@
         <v>241</v>
       </c>
       <c r="L438" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M438" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N438" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M438" s="17" t="s">
+      <c r="O438" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N438" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O438" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P438" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q438">
         <v>2</v>
@@ -20438,19 +20586,19 @@
         <v>241</v>
       </c>
       <c r="L439" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M439" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N439" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M439" s="17" t="s">
+      <c r="O439" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N439" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O439" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P439" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q439">
         <v>2</v>
@@ -20491,19 +20639,19 @@
         <v>241</v>
       </c>
       <c r="L440" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M440" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N440" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M440" s="17" t="s">
+      <c r="O440" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N440" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O440" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P440" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q440">
         <v>2</v>
@@ -20544,19 +20692,19 @@
         <v>241</v>
       </c>
       <c r="L441" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M441" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N441" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M441" s="17" t="s">
+      <c r="O441" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N441" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O441" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P441" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q441">
         <v>2</v>
@@ -20597,19 +20745,19 @@
         <v>241</v>
       </c>
       <c r="L442" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M442" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N442" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M442" s="17" t="s">
+      <c r="O442" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N442" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O442" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P442" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q442">
         <v>2</v>
@@ -20650,19 +20798,19 @@
         <v>241</v>
       </c>
       <c r="L443" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M443" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N443" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M443" s="17" t="s">
+      <c r="O443" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N443" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O443" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P443" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q443">
         <v>2</v>
@@ -20703,19 +20851,19 @@
         <v>241</v>
       </c>
       <c r="L444" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M444" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N444" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M444" s="17" t="s">
+      <c r="O444" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N444" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O444" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P444" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q444">
         <v>2</v>
@@ -20756,19 +20904,19 @@
         <v>241</v>
       </c>
       <c r="L445" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M445" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N445" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M445" s="17" t="s">
+      <c r="O445" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N445" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O445" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P445" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q445">
         <v>2</v>
@@ -20809,19 +20957,19 @@
         <v>241</v>
       </c>
       <c r="L446" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M446" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N446" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M446" s="17" t="s">
+      <c r="O446" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N446" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O446" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P446" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q446">
         <v>2</v>
@@ -20862,19 +21010,19 @@
         <v>241</v>
       </c>
       <c r="L447" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M447" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N447" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M447" s="17" t="s">
+      <c r="O447" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N447" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O447" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P447" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q447">
         <v>2</v>
@@ -20915,19 +21063,19 @@
         <v>241</v>
       </c>
       <c r="L448" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M448" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N448" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M448" s="17" t="s">
+      <c r="O448" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N448" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O448" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P448" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q448">
         <v>2</v>
@@ -20968,19 +21116,19 @@
         <v>241</v>
       </c>
       <c r="L449" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M449" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N449" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M449" s="17" t="s">
+      <c r="O449" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N449" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O449" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P449" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q449">
         <v>2</v>
@@ -21021,19 +21169,19 @@
         <v>241</v>
       </c>
       <c r="L450" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M450" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N450" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M450" s="17" t="s">
+      <c r="O450" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N450" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O450" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P450" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q450">
         <v>2</v>
@@ -21074,19 +21222,19 @@
         <v>241</v>
       </c>
       <c r="L451" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M451" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N451" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M451" s="17" t="s">
+      <c r="O451" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N451" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O451" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P451" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q451">
         <v>2</v>
@@ -21127,19 +21275,19 @@
         <v>241</v>
       </c>
       <c r="L452" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M452" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N452" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M452" s="17" t="s">
+      <c r="O452" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N452" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O452" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P452" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q452">
         <v>2</v>
@@ -21180,19 +21328,19 @@
         <v>241</v>
       </c>
       <c r="L453" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M453" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N453" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M453" s="17" t="s">
+      <c r="O453" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N453" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O453" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P453" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q453">
         <v>2</v>
@@ -21233,19 +21381,19 @@
         <v>241</v>
       </c>
       <c r="L454" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M454" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N454" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M454" s="17" t="s">
+      <c r="O454" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N454" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O454" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P454" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q454">
         <v>2</v>
@@ -21286,19 +21434,19 @@
         <v>241</v>
       </c>
       <c r="L455" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M455" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N455" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M455" s="17" t="s">
+      <c r="O455" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N455" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O455" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P455" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q455">
         <v>2</v>
@@ -21339,19 +21487,19 @@
         <v>241</v>
       </c>
       <c r="L456" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M456" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N456" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M456" s="17" t="s">
+      <c r="O456" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N456" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O456" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P456" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q456">
         <v>2</v>
@@ -21392,19 +21540,19 @@
         <v>241</v>
       </c>
       <c r="L457" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M457" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N457" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M457" s="17" t="s">
+      <c r="O457" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N457" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O457" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P457" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q457">
         <v>2</v>
@@ -21445,19 +21593,19 @@
         <v>241</v>
       </c>
       <c r="L458" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M458" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N458" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M458" s="17" t="s">
+      <c r="O458" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N458" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O458" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P458" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q458">
         <v>2</v>
@@ -21498,19 +21646,19 @@
         <v>241</v>
       </c>
       <c r="L459" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M459" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N459" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M459" s="17" t="s">
+      <c r="O459" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N459" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O459" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P459" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q459">
         <v>2</v>
@@ -21551,19 +21699,19 @@
         <v>241</v>
       </c>
       <c r="L460" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M460" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N460" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M460" s="17" t="s">
+      <c r="O460" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N460" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O460" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P460" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q460">
         <v>2</v>
@@ -21604,19 +21752,19 @@
         <v>241</v>
       </c>
       <c r="L461" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M461" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N461" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M461" s="17" t="s">
+      <c r="O461" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N461" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O461" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P461" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q461">
         <v>2</v>
@@ -21657,19 +21805,19 @@
         <v>241</v>
       </c>
       <c r="L462" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M462" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N462" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M462" s="17" t="s">
+      <c r="O462" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N462" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O462" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P462" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q462">
         <v>2</v>
@@ -21710,19 +21858,19 @@
         <v>241</v>
       </c>
       <c r="L463" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M463" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N463" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M463" s="17" t="s">
+      <c r="O463" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N463" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O463" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P463" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q463">
         <v>2</v>
@@ -21763,19 +21911,19 @@
         <v>241</v>
       </c>
       <c r="L464" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M464" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N464" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M464" s="17" t="s">
+      <c r="O464" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N464" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O464" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P464" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q464">
         <v>2</v>
@@ -21816,19 +21964,19 @@
         <v>241</v>
       </c>
       <c r="L465" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M465" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N465" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M465" s="17" t="s">
+      <c r="O465" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N465" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O465" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P465" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q465">
         <v>2</v>
@@ -21869,19 +22017,19 @@
         <v>241</v>
       </c>
       <c r="L466" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M466" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N466" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M466" s="17" t="s">
+      <c r="O466" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N466" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O466" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P466" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q466">
         <v>2</v>
@@ -21922,19 +22070,19 @@
         <v>241</v>
       </c>
       <c r="L467" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M467" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N467" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M467" s="17" t="s">
+      <c r="O467" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N467" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O467" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P467" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q467">
         <v>2</v>
@@ -21975,19 +22123,19 @@
         <v>241</v>
       </c>
       <c r="L468" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M468" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N468" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M468" s="17" t="s">
+      <c r="O468" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N468" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O468" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P468" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q468">
         <v>2</v>
@@ -22028,19 +22176,19 @@
         <v>241</v>
       </c>
       <c r="L469" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M469" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N469" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M469" s="17" t="s">
+      <c r="O469" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N469" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O469" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P469" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q469">
         <v>2</v>
@@ -22081,19 +22229,19 @@
         <v>241</v>
       </c>
       <c r="L470" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="M470" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="N470" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="M470" s="17" t="s">
+      <c r="O470" s="17" t="s">
         <v>662</v>
       </c>
-      <c r="N470" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="O470" s="17" t="s">
-        <v>664</v>
-      </c>
       <c r="P470" s="17" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Q470">
         <v>2</v>
@@ -22123,7 +22271,7 @@
         <v>60</v>
       </c>
       <c r="H471" s="45" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="I471" s="8">
         <v>2</v>
@@ -22135,19 +22283,19 @@
         <v>241</v>
       </c>
       <c r="L471" s="17" t="s">
+        <v>669</v>
+      </c>
+      <c r="M471" s="17" t="s">
+        <v>670</v>
+      </c>
+      <c r="N471" s="17" t="s">
         <v>671</v>
       </c>
-      <c r="M471" s="17" t="s">
+      <c r="O471" s="17" t="s">
         <v>672</v>
       </c>
-      <c r="N471" s="17" t="s">
-        <v>673</v>
-      </c>
-      <c r="O471" s="17" t="s">
-        <v>674</v>
-      </c>
       <c r="P471" s="17" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="Q471">
         <v>2</v>
@@ -22180,7 +22328,7 @@
         <v>60</v>
       </c>
       <c r="H472" s="45" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="I472" s="8">
         <v>2</v>
@@ -22192,19 +22340,19 @@
         <v>241</v>
       </c>
       <c r="L472" s="17" t="s">
+        <v>669</v>
+      </c>
+      <c r="M472" s="17" t="s">
+        <v>670</v>
+      </c>
+      <c r="N472" s="17" t="s">
         <v>671</v>
       </c>
-      <c r="M472" s="17" t="s">
+      <c r="O472" s="17" t="s">
         <v>672</v>
       </c>
-      <c r="N472" s="17" t="s">
-        <v>673</v>
-      </c>
-      <c r="O472" s="17" t="s">
-        <v>674</v>
-      </c>
       <c r="P472" s="17" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="Q472">
         <v>2</v>
@@ -22237,7 +22385,7 @@
         <v>60</v>
       </c>
       <c r="H473" s="45" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="I473" s="8">
         <v>2</v>
@@ -22249,19 +22397,19 @@
         <v>241</v>
       </c>
       <c r="L473" s="17" t="s">
+        <v>669</v>
+      </c>
+      <c r="M473" s="17" t="s">
+        <v>670</v>
+      </c>
+      <c r="N473" s="17" t="s">
         <v>671</v>
       </c>
-      <c r="M473" s="17" t="s">
+      <c r="O473" s="17" t="s">
         <v>672</v>
       </c>
-      <c r="N473" s="17" t="s">
-        <v>673</v>
-      </c>
-      <c r="O473" s="17" t="s">
-        <v>674</v>
-      </c>
       <c r="P473" s="17" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="Q473">
         <v>2</v>
@@ -22294,7 +22442,7 @@
         <v>60</v>
       </c>
       <c r="H474" s="45" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="I474" s="8">
         <v>2</v>
@@ -22306,19 +22454,19 @@
         <v>241</v>
       </c>
       <c r="L474" s="17" t="s">
+        <v>669</v>
+      </c>
+      <c r="M474" s="17" t="s">
+        <v>670</v>
+      </c>
+      <c r="N474" s="17" t="s">
         <v>671</v>
       </c>
-      <c r="M474" s="17" t="s">
+      <c r="O474" s="17" t="s">
         <v>672</v>
       </c>
-      <c r="N474" s="17" t="s">
-        <v>673</v>
-      </c>
-      <c r="O474" s="17" t="s">
-        <v>674</v>
-      </c>
       <c r="P474" s="17" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="Q474">
         <v>2</v>
@@ -26284,7 +26432,7 @@
     </row>
     <row r="551" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A551" s="3" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B551">
         <v>200001</v>
@@ -26313,19 +26461,19 @@
       <c r="J551"/>
       <c r="K551"/>
       <c r="L551" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M551" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N551" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M551" s="3" t="s">
+      <c r="O551" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N551" s="3" t="s">
+      <c r="P551" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O551" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P551" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q551">
         <v>2</v>
@@ -26366,19 +26514,19 @@
       <c r="J552"/>
       <c r="K552"/>
       <c r="L552" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M552" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N552" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M552" s="3" t="s">
+      <c r="O552" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N552" s="3" t="s">
+      <c r="P552" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O552" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P552" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q552">
         <v>2</v>
@@ -26419,19 +26567,19 @@
       <c r="J553"/>
       <c r="K553"/>
       <c r="L553" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M553" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N553" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M553" s="3" t="s">
+      <c r="O553" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N553" s="3" t="s">
+      <c r="P553" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O553" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P553" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q553">
         <v>2</v>
@@ -26472,19 +26620,19 @@
       <c r="J554"/>
       <c r="K554"/>
       <c r="L554" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M554" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N554" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M554" s="3" t="s">
+      <c r="O554" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N554" s="3" t="s">
+      <c r="P554" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O554" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P554" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q554">
         <v>2</v>
@@ -26525,19 +26673,19 @@
       <c r="J555"/>
       <c r="K555"/>
       <c r="L555" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M555" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N555" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M555" s="3" t="s">
+      <c r="O555" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N555" s="3" t="s">
+      <c r="P555" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O555" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P555" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q555">
         <v>2</v>
@@ -26578,19 +26726,19 @@
       <c r="J556"/>
       <c r="K556"/>
       <c r="L556" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M556" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N556" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M556" s="3" t="s">
+      <c r="O556" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N556" s="3" t="s">
+      <c r="P556" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O556" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P556" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q556">
         <v>2</v>
@@ -26631,19 +26779,19 @@
       <c r="J557"/>
       <c r="K557"/>
       <c r="L557" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M557" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N557" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M557" s="3" t="s">
+      <c r="O557" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N557" s="3" t="s">
+      <c r="P557" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O557" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P557" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q557">
         <v>2</v>
@@ -26684,19 +26832,19 @@
       <c r="J558"/>
       <c r="K558"/>
       <c r="L558" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M558" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N558" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M558" s="3" t="s">
+      <c r="O558" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N558" s="3" t="s">
+      <c r="P558" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O558" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P558" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q558">
         <v>2</v>
@@ -26737,19 +26885,19 @@
       <c r="J559"/>
       <c r="K559"/>
       <c r="L559" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M559" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N559" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M559" s="3" t="s">
+      <c r="O559" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N559" s="3" t="s">
+      <c r="P559" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O559" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P559" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q559">
         <v>2</v>
@@ -26790,19 +26938,19 @@
       <c r="J560"/>
       <c r="K560"/>
       <c r="L560" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M560" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N560" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M560" s="3" t="s">
+      <c r="O560" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N560" s="3" t="s">
+      <c r="P560" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O560" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P560" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q560">
         <v>2</v>
@@ -26843,19 +26991,19 @@
       <c r="J561"/>
       <c r="K561"/>
       <c r="L561" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M561" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N561" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M561" s="3" t="s">
+      <c r="O561" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N561" s="3" t="s">
+      <c r="P561" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O561" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P561" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q561">
         <v>2</v>
@@ -26896,19 +27044,19 @@
       <c r="J562"/>
       <c r="K562"/>
       <c r="L562" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M562" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N562" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M562" s="3" t="s">
+      <c r="O562" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N562" s="3" t="s">
+      <c r="P562" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O562" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P562" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q562">
         <v>2</v>
@@ -26949,19 +27097,19 @@
       <c r="J563"/>
       <c r="K563"/>
       <c r="L563" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M563" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N563" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M563" s="3" t="s">
+      <c r="O563" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N563" s="3" t="s">
+      <c r="P563" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O563" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P563" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q563">
         <v>2</v>
@@ -27002,19 +27150,19 @@
       <c r="J564"/>
       <c r="K564"/>
       <c r="L564" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M564" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N564" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M564" s="3" t="s">
+      <c r="O564" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N564" s="3" t="s">
+      <c r="P564" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O564" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P564" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q564">
         <v>2</v>
@@ -27055,19 +27203,19 @@
       <c r="J565"/>
       <c r="K565"/>
       <c r="L565" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M565" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N565" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M565" s="3" t="s">
+      <c r="O565" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N565" s="3" t="s">
+      <c r="P565" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O565" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P565" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q565">
         <v>2</v>
@@ -27108,19 +27256,19 @@
       <c r="J566"/>
       <c r="K566"/>
       <c r="L566" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M566" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N566" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M566" s="3" t="s">
+      <c r="O566" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N566" s="3" t="s">
+      <c r="P566" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O566" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P566" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q566">
         <v>2</v>
@@ -27161,19 +27309,19 @@
       <c r="J567"/>
       <c r="K567"/>
       <c r="L567" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M567" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N567" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M567" s="3" t="s">
+      <c r="O567" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N567" s="3" t="s">
+      <c r="P567" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O567" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P567" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q567">
         <v>2</v>
@@ -27214,19 +27362,19 @@
       <c r="J568"/>
       <c r="K568"/>
       <c r="L568" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M568" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N568" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M568" s="3" t="s">
+      <c r="O568" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N568" s="3" t="s">
+      <c r="P568" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O568" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P568" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q568">
         <v>2</v>
@@ -27267,19 +27415,19 @@
       <c r="J569"/>
       <c r="K569"/>
       <c r="L569" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M569" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N569" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M569" s="3" t="s">
+      <c r="O569" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N569" s="3" t="s">
+      <c r="P569" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O569" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P569" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q569">
         <v>2</v>
@@ -27320,19 +27468,19 @@
       <c r="J570"/>
       <c r="K570"/>
       <c r="L570" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M570" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N570" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M570" s="3" t="s">
+      <c r="O570" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N570" s="3" t="s">
+      <c r="P570" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O570" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P570" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q570">
         <v>2</v>
@@ -27373,19 +27521,19 @@
       <c r="J571"/>
       <c r="K571"/>
       <c r="L571" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M571" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N571" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M571" s="3" t="s">
+      <c r="O571" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N571" s="3" t="s">
+      <c r="P571" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O571" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P571" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q571">
         <v>2</v>
@@ -27426,19 +27574,19 @@
       <c r="J572"/>
       <c r="K572"/>
       <c r="L572" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M572" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N572" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M572" s="3" t="s">
+      <c r="O572" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N572" s="3" t="s">
+      <c r="P572" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O572" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P572" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q572">
         <v>2</v>
@@ -27479,19 +27627,19 @@
       <c r="J573"/>
       <c r="K573"/>
       <c r="L573" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M573" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N573" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M573" s="3" t="s">
+      <c r="O573" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N573" s="3" t="s">
+      <c r="P573" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O573" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P573" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q573">
         <v>2</v>
@@ -27532,19 +27680,19 @@
       <c r="J574"/>
       <c r="K574"/>
       <c r="L574" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M574" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N574" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M574" s="3" t="s">
+      <c r="O574" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N574" s="3" t="s">
+      <c r="P574" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O574" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P574" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q574">
         <v>2</v>
@@ -27585,19 +27733,19 @@
       <c r="J575"/>
       <c r="K575"/>
       <c r="L575" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M575" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N575" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M575" s="3" t="s">
+      <c r="O575" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N575" s="3" t="s">
+      <c r="P575" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O575" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P575" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q575">
         <v>2</v>
@@ -27638,19 +27786,19 @@
       <c r="J576"/>
       <c r="K576"/>
       <c r="L576" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M576" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N576" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M576" s="3" t="s">
+      <c r="O576" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N576" s="3" t="s">
+      <c r="P576" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O576" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P576" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q576">
         <v>2</v>
@@ -27691,19 +27839,19 @@
       <c r="J577"/>
       <c r="K577"/>
       <c r="L577" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M577" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N577" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M577" s="3" t="s">
+      <c r="O577" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N577" s="3" t="s">
+      <c r="P577" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O577" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P577" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q577">
         <v>2</v>
@@ -27744,19 +27892,19 @@
       <c r="J578"/>
       <c r="K578"/>
       <c r="L578" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M578" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N578" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M578" s="3" t="s">
+      <c r="O578" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N578" s="3" t="s">
+      <c r="P578" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O578" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P578" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q578">
         <v>2</v>
@@ -27797,19 +27945,19 @@
       <c r="J579"/>
       <c r="K579"/>
       <c r="L579" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M579" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N579" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M579" s="3" t="s">
+      <c r="O579" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N579" s="3" t="s">
+      <c r="P579" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O579" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P579" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q579">
         <v>2</v>
@@ -27850,19 +27998,19 @@
       <c r="J580"/>
       <c r="K580"/>
       <c r="L580" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M580" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N580" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M580" s="3" t="s">
+      <c r="O580" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N580" s="3" t="s">
+      <c r="P580" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O580" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P580" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q580">
         <v>2</v>
@@ -27903,19 +28051,19 @@
       <c r="J581"/>
       <c r="K581"/>
       <c r="L581" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M581" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N581" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M581" s="3" t="s">
+      <c r="O581" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N581" s="3" t="s">
+      <c r="P581" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O581" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P581" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q581">
         <v>2</v>
@@ -27956,19 +28104,19 @@
       <c r="J582"/>
       <c r="K582"/>
       <c r="L582" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M582" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N582" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M582" s="3" t="s">
+      <c r="O582" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N582" s="3" t="s">
+      <c r="P582" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O582" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P582" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q582">
         <v>2</v>
@@ -28009,19 +28157,19 @@
       <c r="J583"/>
       <c r="K583"/>
       <c r="L583" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M583" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N583" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M583" s="3" t="s">
+      <c r="O583" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N583" s="3" t="s">
+      <c r="P583" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O583" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P583" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q583">
         <v>2</v>
@@ -28062,19 +28210,19 @@
       <c r="J584"/>
       <c r="K584"/>
       <c r="L584" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M584" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N584" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M584" s="3" t="s">
+      <c r="O584" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N584" s="3" t="s">
+      <c r="P584" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O584" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P584" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q584">
         <v>2</v>
@@ -28115,19 +28263,19 @@
       <c r="J585"/>
       <c r="K585"/>
       <c r="L585" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M585" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N585" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M585" s="3" t="s">
+      <c r="O585" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N585" s="3" t="s">
+      <c r="P585" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O585" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P585" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q585">
         <v>2</v>
@@ -28168,19 +28316,19 @@
       <c r="J586"/>
       <c r="K586"/>
       <c r="L586" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M586" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N586" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M586" s="3" t="s">
+      <c r="O586" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N586" s="3" t="s">
+      <c r="P586" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O586" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P586" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q586">
         <v>2</v>
@@ -28221,19 +28369,19 @@
       <c r="J587"/>
       <c r="K587"/>
       <c r="L587" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M587" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N587" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M587" s="3" t="s">
+      <c r="O587" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N587" s="3" t="s">
+      <c r="P587" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O587" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P587" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q587">
         <v>2</v>
@@ -28274,19 +28422,19 @@
       <c r="J588"/>
       <c r="K588"/>
       <c r="L588" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M588" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N588" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M588" s="3" t="s">
+      <c r="O588" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N588" s="3" t="s">
+      <c r="P588" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O588" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P588" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q588">
         <v>2</v>
@@ -28327,19 +28475,19 @@
       <c r="J589"/>
       <c r="K589"/>
       <c r="L589" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M589" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N589" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M589" s="3" t="s">
+      <c r="O589" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N589" s="3" t="s">
+      <c r="P589" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O589" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P589" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q589">
         <v>2</v>
@@ -28380,19 +28528,19 @@
       <c r="J590"/>
       <c r="K590"/>
       <c r="L590" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M590" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N590" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M590" s="3" t="s">
+      <c r="O590" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N590" s="3" t="s">
+      <c r="P590" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O590" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P590" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q590">
         <v>2</v>
@@ -28433,19 +28581,19 @@
       <c r="J591"/>
       <c r="K591"/>
       <c r="L591" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M591" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N591" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M591" s="3" t="s">
+      <c r="O591" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N591" s="3" t="s">
+      <c r="P591" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O591" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P591" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q591">
         <v>2</v>
@@ -28486,19 +28634,19 @@
       <c r="J592"/>
       <c r="K592"/>
       <c r="L592" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M592" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N592" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M592" s="3" t="s">
+      <c r="O592" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N592" s="3" t="s">
+      <c r="P592" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O592" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P592" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q592">
         <v>2</v>
@@ -28539,19 +28687,19 @@
       <c r="J593"/>
       <c r="K593"/>
       <c r="L593" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M593" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N593" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M593" s="3" t="s">
+      <c r="O593" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N593" s="3" t="s">
+      <c r="P593" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O593" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P593" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q593">
         <v>2</v>
@@ -28592,19 +28740,19 @@
       <c r="J594"/>
       <c r="K594"/>
       <c r="L594" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M594" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N594" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M594" s="3" t="s">
+      <c r="O594" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N594" s="3" t="s">
+      <c r="P594" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O594" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P594" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q594">
         <v>2</v>
@@ -28645,19 +28793,19 @@
       <c r="J595"/>
       <c r="K595"/>
       <c r="L595" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M595" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N595" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M595" s="3" t="s">
+      <c r="O595" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N595" s="3" t="s">
+      <c r="P595" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O595" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P595" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q595">
         <v>2</v>
@@ -28695,19 +28843,19 @@
         <v>1</v>
       </c>
       <c r="L596" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M596" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N596" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M596" s="3" t="s">
+      <c r="O596" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N596" s="3" t="s">
+      <c r="P596" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O596" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P596" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q596">
         <v>2</v>
@@ -28742,19 +28890,19 @@
         <v>1</v>
       </c>
       <c r="L597" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M597" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N597" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M597" s="3" t="s">
+      <c r="O597" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N597" s="3" t="s">
+      <c r="P597" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O597" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P597" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q597">
         <v>2</v>
@@ -28789,19 +28937,19 @@
         <v>1</v>
       </c>
       <c r="L598" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M598" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N598" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M598" s="3" t="s">
+      <c r="O598" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N598" s="3" t="s">
+      <c r="P598" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O598" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P598" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q598">
         <v>2</v>
@@ -28836,19 +28984,19 @@
         <v>1</v>
       </c>
       <c r="L599" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M599" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N599" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M599" s="3" t="s">
+      <c r="O599" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N599" s="3" t="s">
+      <c r="P599" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O599" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P599" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q599">
         <v>2</v>
@@ -28883,19 +29031,19 @@
         <v>1</v>
       </c>
       <c r="L600" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M600" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N600" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M600" s="3" t="s">
+      <c r="O600" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N600" s="3" t="s">
+      <c r="P600" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O600" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P600" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q600">
         <v>2</v>
@@ -28930,19 +29078,19 @@
         <v>1</v>
       </c>
       <c r="L601" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M601" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N601" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M601" s="3" t="s">
+      <c r="O601" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N601" s="3" t="s">
+      <c r="P601" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O601" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P601" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q601">
         <v>2</v>
@@ -28977,19 +29125,19 @@
         <v>1</v>
       </c>
       <c r="L602" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M602" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N602" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M602" s="3" t="s">
+      <c r="O602" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N602" s="3" t="s">
+      <c r="P602" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O602" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P602" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q602">
         <v>2</v>
@@ -29024,19 +29172,19 @@
         <v>1</v>
       </c>
       <c r="L603" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M603" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N603" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M603" s="3" t="s">
+      <c r="O603" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N603" s="3" t="s">
+      <c r="P603" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O603" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P603" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q603">
         <v>2</v>
@@ -29071,19 +29219,19 @@
         <v>1</v>
       </c>
       <c r="L604" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M604" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N604" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M604" s="3" t="s">
+      <c r="O604" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N604" s="3" t="s">
+      <c r="P604" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O604" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P604" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q604">
         <v>2</v>
@@ -29118,19 +29266,19 @@
         <v>1</v>
       </c>
       <c r="L605" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M605" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N605" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M605" s="3" t="s">
+      <c r="O605" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N605" s="3" t="s">
+      <c r="P605" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O605" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P605" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q605">
         <v>2</v>
@@ -29165,19 +29313,19 @@
         <v>1</v>
       </c>
       <c r="L606" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M606" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N606" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M606" s="3" t="s">
+      <c r="O606" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N606" s="3" t="s">
+      <c r="P606" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O606" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P606" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q606">
         <v>2</v>
@@ -29215,19 +29363,19 @@
       <c r="J607"/>
       <c r="K607"/>
       <c r="L607" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M607" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N607" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M607" s="3" t="s">
+      <c r="O607" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N607" s="3" t="s">
+      <c r="P607" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O607" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P607" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q607">
         <v>2</v>
@@ -29268,19 +29416,19 @@
       <c r="J608"/>
       <c r="K608"/>
       <c r="L608" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M608" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N608" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M608" s="3" t="s">
+      <c r="O608" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N608" s="3" t="s">
+      <c r="P608" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O608" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P608" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q608">
         <v>2</v>
@@ -29321,19 +29469,19 @@
       <c r="J609"/>
       <c r="K609"/>
       <c r="L609" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M609" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N609" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M609" s="3" t="s">
+      <c r="O609" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N609" s="3" t="s">
+      <c r="P609" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O609" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P609" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q609">
         <v>2</v>
@@ -29374,19 +29522,19 @@
       <c r="J610"/>
       <c r="K610"/>
       <c r="L610" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M610" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N610" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M610" s="3" t="s">
+      <c r="O610" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N610" s="3" t="s">
+      <c r="P610" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O610" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P610" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q610">
         <v>2</v>
@@ -29427,19 +29575,19 @@
       <c r="J611"/>
       <c r="K611"/>
       <c r="L611" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M611" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N611" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M611" s="3" t="s">
+      <c r="O611" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N611" s="3" t="s">
+      <c r="P611" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O611" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P611" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q611">
         <v>2</v>
@@ -29480,19 +29628,19 @@
       <c r="J612"/>
       <c r="K612"/>
       <c r="L612" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M612" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N612" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M612" s="3" t="s">
+      <c r="O612" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N612" s="3" t="s">
+      <c r="P612" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O612" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P612" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q612">
         <v>2</v>
@@ -29533,19 +29681,19 @@
       <c r="J613"/>
       <c r="K613"/>
       <c r="L613" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M613" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N613" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M613" s="3" t="s">
+      <c r="O613" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N613" s="3" t="s">
+      <c r="P613" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O613" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P613" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q613">
         <v>2</v>
@@ -29586,19 +29734,19 @@
       <c r="J614"/>
       <c r="K614"/>
       <c r="L614" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M614" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N614" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M614" s="3" t="s">
+      <c r="O614" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N614" s="3" t="s">
+      <c r="P614" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O614" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P614" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q614">
         <v>2</v>
@@ -29639,19 +29787,19 @@
       <c r="J615"/>
       <c r="K615"/>
       <c r="L615" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M615" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N615" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M615" s="3" t="s">
+      <c r="O615" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N615" s="3" t="s">
+      <c r="P615" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O615" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P615" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q615">
         <v>2</v>
@@ -29689,19 +29837,19 @@
         <v>1</v>
       </c>
       <c r="L616" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M616" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N616" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M616" s="3" t="s">
+      <c r="O616" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N616" s="3" t="s">
+      <c r="P616" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O616" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P616" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q616">
         <v>2</v>
@@ -29736,19 +29884,19 @@
         <v>1</v>
       </c>
       <c r="L617" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M617" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N617" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M617" s="3" t="s">
+      <c r="O617" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N617" s="3" t="s">
+      <c r="P617" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O617" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P617" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q617">
         <v>2</v>
@@ -29783,19 +29931,19 @@
         <v>1</v>
       </c>
       <c r="L618" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M618" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N618" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M618" s="3" t="s">
+      <c r="O618" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N618" s="3" t="s">
+      <c r="P618" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O618" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P618" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q618">
         <v>2</v>
@@ -29830,19 +29978,19 @@
         <v>1</v>
       </c>
       <c r="L619" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M619" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N619" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="M619" s="3" t="s">
+      <c r="O619" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="N619" s="3" t="s">
+      <c r="P619" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="O619" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P619" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="Q619">
         <v>2</v>
@@ -37940,7 +38088,7 @@
     </row>
     <row r="795" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A795" s="3" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B795">
         <v>20000100</v>
@@ -37967,19 +38115,19 @@
         <v>1</v>
       </c>
       <c r="L795" s="21" t="s">
+        <v>450</v>
+      </c>
+      <c r="M795" s="21" t="s">
+        <v>451</v>
+      </c>
+      <c r="N795" s="21" t="s">
         <v>452</v>
       </c>
-      <c r="M795" s="21" t="s">
+      <c r="O795" s="21" t="s">
         <v>453</v>
       </c>
-      <c r="N795" s="21" t="s">
+      <c r="P795" s="21" t="s">
         <v>454</v>
-      </c>
-      <c r="O795" s="21" t="s">
-        <v>455</v>
-      </c>
-      <c r="P795" s="21" t="s">
-        <v>456</v>
       </c>
       <c r="Q795">
         <v>3</v>
@@ -38014,19 +38162,19 @@
         <v>1</v>
       </c>
       <c r="L796" s="21" t="s">
+        <v>450</v>
+      </c>
+      <c r="M796" s="21" t="s">
+        <v>451</v>
+      </c>
+      <c r="N796" s="21" t="s">
         <v>452</v>
       </c>
-      <c r="M796" s="21" t="s">
+      <c r="O796" s="21" t="s">
         <v>453</v>
       </c>
-      <c r="N796" s="21" t="s">
+      <c r="P796" s="21" t="s">
         <v>454</v>
-      </c>
-      <c r="O796" s="21" t="s">
-        <v>455</v>
-      </c>
-      <c r="P796" s="21" t="s">
-        <v>456</v>
       </c>
       <c r="Q796">
         <v>3</v>
@@ -38061,19 +38209,19 @@
         <v>1</v>
       </c>
       <c r="L797" s="21" t="s">
+        <v>450</v>
+      </c>
+      <c r="M797" s="21" t="s">
+        <v>451</v>
+      </c>
+      <c r="N797" s="21" t="s">
         <v>452</v>
       </c>
-      <c r="M797" s="21" t="s">
+      <c r="O797" s="21" t="s">
         <v>453</v>
       </c>
-      <c r="N797" s="21" t="s">
+      <c r="P797" s="21" t="s">
         <v>454</v>
-      </c>
-      <c r="O797" s="21" t="s">
-        <v>455</v>
-      </c>
-      <c r="P797" s="21" t="s">
-        <v>456</v>
       </c>
       <c r="Q797">
         <v>3</v>
@@ -38108,19 +38256,19 @@
         <v>1</v>
       </c>
       <c r="L798" s="21" t="s">
+        <v>450</v>
+      </c>
+      <c r="M798" s="21" t="s">
+        <v>451</v>
+      </c>
+      <c r="N798" s="21" t="s">
         <v>452</v>
       </c>
-      <c r="M798" s="21" t="s">
+      <c r="O798" s="21" t="s">
         <v>453</v>
       </c>
-      <c r="N798" s="21" t="s">
+      <c r="P798" s="21" t="s">
         <v>454</v>
-      </c>
-      <c r="O798" s="21" t="s">
-        <v>455</v>
-      </c>
-      <c r="P798" s="21" t="s">
-        <v>456</v>
       </c>
       <c r="Q798">
         <v>3</v>
@@ -38131,7 +38279,7 @@
     </row>
     <row r="799" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A799" s="3" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B799">
         <v>200012</v>
@@ -38158,19 +38306,19 @@
         <v>1</v>
       </c>
       <c r="L799" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="M799" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="M799" s="1" t="s">
+      <c r="N799" s="19" t="s">
+        <v>469</v>
+      </c>
+      <c r="O799" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="N799" s="19" t="s">
-        <v>471</v>
-      </c>
-      <c r="O799" s="1" t="s">
-        <v>462</v>
-      </c>
       <c r="P799" s="19" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="Q799">
         <v>3</v>
@@ -38205,19 +38353,19 @@
         <v>1</v>
       </c>
       <c r="L800" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="M800" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="M800" s="1" t="s">
+      <c r="N800" s="19" t="s">
+        <v>469</v>
+      </c>
+      <c r="O800" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="N800" s="19" t="s">
-        <v>471</v>
-      </c>
-      <c r="O800" s="1" t="s">
-        <v>462</v>
-      </c>
       <c r="P800" s="19" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="Q800">
         <v>3</v>
@@ -38252,19 +38400,19 @@
         <v>1</v>
       </c>
       <c r="L801" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="M801" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="M801" s="1" t="s">
+      <c r="N801" s="19" t="s">
+        <v>469</v>
+      </c>
+      <c r="O801" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="N801" s="19" t="s">
-        <v>471</v>
-      </c>
-      <c r="O801" s="1" t="s">
-        <v>462</v>
-      </c>
       <c r="P801" s="19" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="Q801">
         <v>3</v>
@@ -38299,19 +38447,19 @@
         <v>1</v>
       </c>
       <c r="L802" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="M802" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="M802" s="1" t="s">
+      <c r="N802" s="19" t="s">
+        <v>469</v>
+      </c>
+      <c r="O802" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="N802" s="19" t="s">
-        <v>471</v>
-      </c>
-      <c r="O802" s="1" t="s">
-        <v>462</v>
-      </c>
       <c r="P802" s="19" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="Q802">
         <v>3</v>
@@ -38346,19 +38494,19 @@
         <v>1</v>
       </c>
       <c r="L803" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="M803" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="M803" s="1" t="s">
+      <c r="N803" s="19" t="s">
+        <v>471</v>
+      </c>
+      <c r="O803" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="N803" s="19" t="s">
-        <v>473</v>
-      </c>
-      <c r="O803" s="1" t="s">
-        <v>463</v>
-      </c>
       <c r="P803" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="Q803">
         <v>3</v>
@@ -38393,19 +38541,19 @@
         <v>1</v>
       </c>
       <c r="L804" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="M804" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="M804" s="1" t="s">
+      <c r="N804" s="19" t="s">
+        <v>471</v>
+      </c>
+      <c r="O804" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="N804" s="19" t="s">
-        <v>473</v>
-      </c>
-      <c r="O804" s="1" t="s">
-        <v>463</v>
-      </c>
       <c r="P804" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="Q804">
         <v>3</v>
@@ -38416,7 +38564,7 @@
     </row>
     <row r="805" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A805" s="3" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B805">
         <v>200003</v>
@@ -38443,19 +38591,19 @@
         <v>1</v>
       </c>
       <c r="L805" s="21" t="s">
+        <v>473</v>
+      </c>
+      <c r="M805" s="22" t="s">
+        <v>474</v>
+      </c>
+      <c r="N805" s="13" t="s">
         <v>475</v>
       </c>
-      <c r="M805" s="22" t="s">
-        <v>476</v>
-      </c>
-      <c r="N805" s="13" t="s">
-        <v>477</v>
-      </c>
       <c r="O805" s="13" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="P805" s="24" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="Q805">
         <v>3</v>
@@ -38490,19 +38638,19 @@
         <v>1</v>
       </c>
       <c r="L806" s="21" t="s">
+        <v>473</v>
+      </c>
+      <c r="M806" s="22" t="s">
+        <v>474</v>
+      </c>
+      <c r="N806" s="13" t="s">
         <v>475</v>
       </c>
-      <c r="M806" s="22" t="s">
-        <v>476</v>
-      </c>
-      <c r="N806" s="13" t="s">
-        <v>477</v>
-      </c>
       <c r="O806" s="13" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="P806" s="24" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="Q806">
         <v>3</v>
@@ -38537,19 +38685,19 @@
         <v>1</v>
       </c>
       <c r="L807" s="21" t="s">
+        <v>473</v>
+      </c>
+      <c r="M807" s="22" t="s">
+        <v>474</v>
+      </c>
+      <c r="N807" s="13" t="s">
         <v>475</v>
       </c>
-      <c r="M807" s="22" t="s">
-        <v>476</v>
-      </c>
-      <c r="N807" s="13" t="s">
-        <v>477</v>
-      </c>
       <c r="O807" s="13" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="P807" s="24" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="Q807">
         <v>3</v>
@@ -38584,19 +38732,19 @@
         <v>1</v>
       </c>
       <c r="L808" s="21" t="s">
+        <v>473</v>
+      </c>
+      <c r="M808" s="22" t="s">
+        <v>474</v>
+      </c>
+      <c r="N808" s="13" t="s">
         <v>475</v>
       </c>
-      <c r="M808" s="22" t="s">
-        <v>476</v>
-      </c>
-      <c r="N808" s="13" t="s">
-        <v>477</v>
-      </c>
       <c r="O808" s="13" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="P808" s="24" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="Q808">
         <v>3</v>
@@ -38607,7 +38755,7 @@
     </row>
     <row r="809" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A809" s="3" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B809">
         <v>200029</v>
@@ -38634,19 +38782,19 @@
         <v>1</v>
       </c>
       <c r="L809" s="25" t="s">
+        <v>498</v>
+      </c>
+      <c r="M809" s="25" t="s">
+        <v>499</v>
+      </c>
+      <c r="N809" s="26" t="s">
         <v>500</v>
       </c>
-      <c r="M809" s="25" t="s">
+      <c r="O809" s="26" t="s">
         <v>501</v>
       </c>
-      <c r="N809" s="26" t="s">
+      <c r="P809" s="26" t="s">
         <v>502</v>
-      </c>
-      <c r="O809" s="26" t="s">
-        <v>503</v>
-      </c>
-      <c r="P809" s="26" t="s">
-        <v>504</v>
       </c>
       <c r="Q809">
         <v>3</v>
@@ -38681,19 +38829,19 @@
         <v>1</v>
       </c>
       <c r="L810" s="25" t="s">
+        <v>498</v>
+      </c>
+      <c r="M810" s="25" t="s">
+        <v>499</v>
+      </c>
+      <c r="N810" s="26" t="s">
         <v>500</v>
       </c>
-      <c r="M810" s="25" t="s">
+      <c r="O810" s="26" t="s">
         <v>501</v>
       </c>
-      <c r="N810" s="26" t="s">
+      <c r="P810" s="26" t="s">
         <v>502</v>
-      </c>
-      <c r="O810" s="26" t="s">
-        <v>503</v>
-      </c>
-      <c r="P810" s="26" t="s">
-        <v>504</v>
       </c>
       <c r="Q810">
         <v>3</v>
@@ -38704,7 +38852,7 @@
     </row>
     <row r="811" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A811" s="3" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B811">
         <v>200024</v>
@@ -38731,19 +38879,19 @@
         <v>1</v>
       </c>
       <c r="L811" s="25" t="s">
+        <v>504</v>
+      </c>
+      <c r="M811" s="25" t="s">
+        <v>505</v>
+      </c>
+      <c r="N811" s="21" t="s">
+        <v>511</v>
+      </c>
+      <c r="O811" s="27" t="s">
         <v>506</v>
       </c>
-      <c r="M811" s="25" t="s">
+      <c r="P811" s="27" t="s">
         <v>507</v>
-      </c>
-      <c r="N811" s="21" t="s">
-        <v>513</v>
-      </c>
-      <c r="O811" s="27" t="s">
-        <v>508</v>
-      </c>
-      <c r="P811" s="27" t="s">
-        <v>509</v>
       </c>
       <c r="Q811">
         <v>3</v>
@@ -38778,19 +38926,19 @@
         <v>1</v>
       </c>
       <c r="L812" s="25" t="s">
+        <v>504</v>
+      </c>
+      <c r="M812" s="25" t="s">
+        <v>505</v>
+      </c>
+      <c r="N812" s="21" t="s">
+        <v>511</v>
+      </c>
+      <c r="O812" s="27" t="s">
         <v>506</v>
       </c>
-      <c r="M812" s="25" t="s">
+      <c r="P812" s="27" t="s">
         <v>507</v>
-      </c>
-      <c r="N812" s="21" t="s">
-        <v>513</v>
-      </c>
-      <c r="O812" s="27" t="s">
-        <v>508</v>
-      </c>
-      <c r="P812" s="27" t="s">
-        <v>509</v>
       </c>
       <c r="Q812">
         <v>3</v>
@@ -38825,19 +38973,19 @@
         <v>1</v>
       </c>
       <c r="L813" s="25" t="s">
+        <v>504</v>
+      </c>
+      <c r="M813" s="25" t="s">
+        <v>505</v>
+      </c>
+      <c r="N813" s="21" t="s">
+        <v>511</v>
+      </c>
+      <c r="O813" s="27" t="s">
         <v>506</v>
       </c>
-      <c r="M813" s="25" t="s">
+      <c r="P813" s="27" t="s">
         <v>507</v>
-      </c>
-      <c r="N813" s="21" t="s">
-        <v>513</v>
-      </c>
-      <c r="O813" s="27" t="s">
-        <v>508</v>
-      </c>
-      <c r="P813" s="27" t="s">
-        <v>509</v>
       </c>
       <c r="Q813">
         <v>3</v>
@@ -38848,7 +38996,7 @@
     </row>
     <row r="814" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A814" s="3" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B814" s="28">
         <v>20000108</v>
@@ -38875,19 +39023,19 @@
         <v>1</v>
       </c>
       <c r="L814" s="21" t="s">
+        <v>533</v>
+      </c>
+      <c r="M814" s="21" t="s">
+        <v>534</v>
+      </c>
+      <c r="N814" s="21" t="s">
+        <v>532</v>
+      </c>
+      <c r="O814" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="M814" s="21" t="s">
+      <c r="P814" s="30" t="s">
         <v>536</v>
-      </c>
-      <c r="N814" s="21" t="s">
-        <v>534</v>
-      </c>
-      <c r="O814" s="3" t="s">
-        <v>537</v>
-      </c>
-      <c r="P814" s="30" t="s">
-        <v>538</v>
       </c>
       <c r="Q814">
         <v>3</v>
@@ -38922,19 +39070,19 @@
         <v>1</v>
       </c>
       <c r="L815" s="21" t="s">
+        <v>533</v>
+      </c>
+      <c r="M815" s="21" t="s">
+        <v>534</v>
+      </c>
+      <c r="N815" s="21" t="s">
+        <v>532</v>
+      </c>
+      <c r="O815" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="M815" s="21" t="s">
+      <c r="P815" s="30" t="s">
         <v>536</v>
-      </c>
-      <c r="N815" s="21" t="s">
-        <v>534</v>
-      </c>
-      <c r="O815" s="3" t="s">
-        <v>537</v>
-      </c>
-      <c r="P815" s="30" t="s">
-        <v>538</v>
       </c>
       <c r="Q815">
         <v>3</v>
@@ -38969,19 +39117,19 @@
         <v>1</v>
       </c>
       <c r="L816" s="21" t="s">
+        <v>533</v>
+      </c>
+      <c r="M816" s="21" t="s">
+        <v>534</v>
+      </c>
+      <c r="N816" s="21" t="s">
+        <v>532</v>
+      </c>
+      <c r="O816" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="M816" s="21" t="s">
+      <c r="P816" s="30" t="s">
         <v>536</v>
-      </c>
-      <c r="N816" s="21" t="s">
-        <v>534</v>
-      </c>
-      <c r="O816" s="3" t="s">
-        <v>537</v>
-      </c>
-      <c r="P816" s="30" t="s">
-        <v>538</v>
       </c>
       <c r="Q816">
         <v>3</v>
@@ -39016,19 +39164,19 @@
         <v>1</v>
       </c>
       <c r="L817" s="21" t="s">
+        <v>533</v>
+      </c>
+      <c r="M817" s="21" t="s">
+        <v>534</v>
+      </c>
+      <c r="N817" s="21" t="s">
+        <v>532</v>
+      </c>
+      <c r="O817" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="M817" s="21" t="s">
+      <c r="P817" s="30" t="s">
         <v>536</v>
-      </c>
-      <c r="N817" s="21" t="s">
-        <v>534</v>
-      </c>
-      <c r="O817" s="3" t="s">
-        <v>537</v>
-      </c>
-      <c r="P817" s="30" t="s">
-        <v>538</v>
       </c>
       <c r="Q817">
         <v>3</v>
@@ -39039,7 +39187,7 @@
     </row>
     <row r="818" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A818" s="3" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B818">
         <v>200021</v>
@@ -39066,19 +39214,19 @@
         <v>1</v>
       </c>
       <c r="L818" s="25" t="s">
+        <v>563</v>
+      </c>
+      <c r="M818" s="25" t="s">
+        <v>564</v>
+      </c>
+      <c r="N818" s="33" t="s">
         <v>565</v>
       </c>
-      <c r="M818" s="25" t="s">
+      <c r="O818" s="33" t="s">
         <v>566</v>
       </c>
-      <c r="N818" s="33" t="s">
+      <c r="P818" s="33" t="s">
         <v>567</v>
-      </c>
-      <c r="O818" s="33" t="s">
-        <v>568</v>
-      </c>
-      <c r="P818" s="33" t="s">
-        <v>569</v>
       </c>
       <c r="Q818">
         <v>3</v>
@@ -39113,19 +39261,19 @@
         <v>1</v>
       </c>
       <c r="L819" s="25" t="s">
+        <v>563</v>
+      </c>
+      <c r="M819" s="25" t="s">
+        <v>564</v>
+      </c>
+      <c r="N819" s="33" t="s">
         <v>565</v>
       </c>
-      <c r="M819" s="25" t="s">
+      <c r="O819" s="33" t="s">
         <v>566</v>
       </c>
-      <c r="N819" s="33" t="s">
+      <c r="P819" s="33" t="s">
         <v>567</v>
-      </c>
-      <c r="O819" s="33" t="s">
-        <v>568</v>
-      </c>
-      <c r="P819" s="33" t="s">
-        <v>569</v>
       </c>
       <c r="Q819">
         <v>3</v>
@@ -39160,19 +39308,19 @@
         <v>1</v>
       </c>
       <c r="L820" s="25" t="s">
+        <v>563</v>
+      </c>
+      <c r="M820" s="25" t="s">
+        <v>564</v>
+      </c>
+      <c r="N820" s="33" t="s">
         <v>565</v>
       </c>
-      <c r="M820" s="25" t="s">
+      <c r="O820" s="33" t="s">
         <v>566</v>
       </c>
-      <c r="N820" s="33" t="s">
+      <c r="P820" s="33" t="s">
         <v>567</v>
-      </c>
-      <c r="O820" s="33" t="s">
-        <v>568</v>
-      </c>
-      <c r="P820" s="33" t="s">
-        <v>569</v>
       </c>
       <c r="Q820">
         <v>3</v>
@@ -39183,7 +39331,7 @@
     </row>
     <row r="821" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A821" s="3" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B821">
         <v>200083</v>
@@ -39210,19 +39358,19 @@
         <v>1</v>
       </c>
       <c r="L821" s="36" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="M821" s="36" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="N821" s="34" t="s">
+        <v>579</v>
+      </c>
+      <c r="O821" s="35" t="s">
+        <v>580</v>
+      </c>
+      <c r="P821" s="35" t="s">
         <v>581</v>
-      </c>
-      <c r="O821" s="35" t="s">
-        <v>582</v>
-      </c>
-      <c r="P821" s="35" t="s">
-        <v>583</v>
       </c>
       <c r="Q821">
         <v>3</v>
@@ -39257,19 +39405,19 @@
         <v>1</v>
       </c>
       <c r="L822" s="36" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="M822" s="36" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="N822" s="34" t="s">
+        <v>579</v>
+      </c>
+      <c r="O822" s="35" t="s">
+        <v>580</v>
+      </c>
+      <c r="P822" s="35" t="s">
         <v>581</v>
-      </c>
-      <c r="O822" s="35" t="s">
-        <v>582</v>
-      </c>
-      <c r="P822" s="35" t="s">
-        <v>583</v>
       </c>
       <c r="Q822">
         <v>3</v>
@@ -39304,19 +39452,19 @@
         <v>1</v>
       </c>
       <c r="L823" s="36" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="M823" s="36" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="N823" s="34" t="s">
+        <v>579</v>
+      </c>
+      <c r="O823" s="35" t="s">
+        <v>580</v>
+      </c>
+      <c r="P823" s="35" t="s">
         <v>581</v>
-      </c>
-      <c r="O823" s="35" t="s">
-        <v>582</v>
-      </c>
-      <c r="P823" s="35" t="s">
-        <v>583</v>
       </c>
       <c r="Q823">
         <v>3</v>
@@ -39327,7 +39475,7 @@
     </row>
     <row r="824" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A824" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B824">
         <v>200001</v>
@@ -39354,19 +39502,19 @@
         <v>1</v>
       </c>
       <c r="L824" s="17" t="s">
+        <v>593</v>
+      </c>
+      <c r="M824" s="17" t="s">
+        <v>594</v>
+      </c>
+      <c r="N824" s="37" t="s">
         <v>595</v>
       </c>
-      <c r="M824" s="17" t="s">
+      <c r="O824" s="37" t="s">
         <v>596</v>
       </c>
-      <c r="N824" s="37" t="s">
+      <c r="P824" s="37" t="s">
         <v>597</v>
-      </c>
-      <c r="O824" s="37" t="s">
-        <v>598</v>
-      </c>
-      <c r="P824" s="37" t="s">
-        <v>599</v>
       </c>
       <c r="Q824">
         <v>3</v>
@@ -39401,19 +39549,19 @@
         <v>1</v>
       </c>
       <c r="L825" s="17" t="s">
+        <v>593</v>
+      </c>
+      <c r="M825" s="17" t="s">
+        <v>594</v>
+      </c>
+      <c r="N825" s="37" t="s">
         <v>595</v>
       </c>
-      <c r="M825" s="17" t="s">
+      <c r="O825" s="37" t="s">
         <v>596</v>
       </c>
-      <c r="N825" s="37" t="s">
+      <c r="P825" s="37" t="s">
         <v>597</v>
-      </c>
-      <c r="O825" s="37" t="s">
-        <v>598</v>
-      </c>
-      <c r="P825" s="37" t="s">
-        <v>599</v>
       </c>
       <c r="Q825">
         <v>3</v>
@@ -39448,19 +39596,19 @@
         <v>1</v>
       </c>
       <c r="L826" s="17" t="s">
+        <v>593</v>
+      </c>
+      <c r="M826" s="17" t="s">
+        <v>594</v>
+      </c>
+      <c r="N826" s="37" t="s">
         <v>595</v>
       </c>
-      <c r="M826" s="17" t="s">
+      <c r="O826" s="37" t="s">
         <v>596</v>
       </c>
-      <c r="N826" s="37" t="s">
+      <c r="P826" s="37" t="s">
         <v>597</v>
-      </c>
-      <c r="O826" s="37" t="s">
-        <v>598</v>
-      </c>
-      <c r="P826" s="37" t="s">
-        <v>599</v>
       </c>
       <c r="Q826">
         <v>3</v>
@@ -39495,19 +39643,19 @@
         <v>1</v>
       </c>
       <c r="L827" s="17" t="s">
+        <v>593</v>
+      </c>
+      <c r="M827" s="17" t="s">
+        <v>594</v>
+      </c>
+      <c r="N827" s="37" t="s">
         <v>595</v>
       </c>
-      <c r="M827" s="17" t="s">
+      <c r="O827" s="37" t="s">
         <v>596</v>
       </c>
-      <c r="N827" s="37" t="s">
+      <c r="P827" s="37" t="s">
         <v>597</v>
-      </c>
-      <c r="O827" s="37" t="s">
-        <v>598</v>
-      </c>
-      <c r="P827" s="37" t="s">
-        <v>599</v>
       </c>
       <c r="Q827">
         <v>3</v>
@@ -39518,7 +39666,7 @@
     </row>
     <row r="828" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A828" s="3" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B828">
         <v>20000112</v>
@@ -39545,19 +39693,19 @@
         <v>1</v>
       </c>
       <c r="L828" s="41" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="M828" s="40" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="N828" s="38" t="s">
+        <v>628</v>
+      </c>
+      <c r="O828" s="38" t="s">
+        <v>629</v>
+      </c>
+      <c r="P828" s="38" t="s">
         <v>630</v>
-      </c>
-      <c r="O828" s="38" t="s">
-        <v>631</v>
-      </c>
-      <c r="P828" s="38" t="s">
-        <v>632</v>
       </c>
       <c r="Q828">
         <v>3</v>
@@ -39592,19 +39740,19 @@
         <v>1</v>
       </c>
       <c r="L829" s="39" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="M829" s="40" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="N829" s="38" t="s">
+        <v>625</v>
+      </c>
+      <c r="O829" s="38" t="s">
+        <v>626</v>
+      </c>
+      <c r="P829" s="38" t="s">
         <v>627</v>
-      </c>
-      <c r="O829" s="38" t="s">
-        <v>628</v>
-      </c>
-      <c r="P829" s="38" t="s">
-        <v>629</v>
       </c>
       <c r="Q829">
         <v>3</v>
@@ -39639,19 +39787,19 @@
         <v>1</v>
       </c>
       <c r="L830" s="39" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="M830" s="40" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="N830" s="38" t="s">
+        <v>625</v>
+      </c>
+      <c r="O830" s="38" t="s">
+        <v>626</v>
+      </c>
+      <c r="P830" s="38" t="s">
         <v>627</v>
-      </c>
-      <c r="O830" s="38" t="s">
-        <v>628</v>
-      </c>
-      <c r="P830" s="38" t="s">
-        <v>629</v>
       </c>
       <c r="Q830">
         <v>3</v>
@@ -39686,19 +39834,19 @@
         <v>1</v>
       </c>
       <c r="L831" s="39" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="M831" s="40" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="N831" s="38" t="s">
+        <v>625</v>
+      </c>
+      <c r="O831" s="38" t="s">
+        <v>626</v>
+      </c>
+      <c r="P831" s="38" t="s">
         <v>627</v>
-      </c>
-      <c r="O831" s="38" t="s">
-        <v>628</v>
-      </c>
-      <c r="P831" s="38" t="s">
-        <v>629</v>
       </c>
       <c r="Q831">
         <v>3</v>
@@ -39733,19 +39881,19 @@
         <v>1</v>
       </c>
       <c r="L832" s="39" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="M832" s="40" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="N832" s="38" t="s">
+        <v>625</v>
+      </c>
+      <c r="O832" s="38" t="s">
+        <v>626</v>
+      </c>
+      <c r="P832" s="38" t="s">
         <v>627</v>
-      </c>
-      <c r="O832" s="38" t="s">
-        <v>628</v>
-      </c>
-      <c r="P832" s="38" t="s">
-        <v>629</v>
       </c>
       <c r="Q832">
         <v>3</v>
@@ -39756,7 +39904,7 @@
     </row>
     <row r="833" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A833" s="3" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B833">
         <v>200007</v>
@@ -39783,19 +39931,19 @@
         <v>1</v>
       </c>
       <c r="L833" s="28" t="s">
+        <v>663</v>
+      </c>
+      <c r="M833" s="37" t="s">
+        <v>664</v>
+      </c>
+      <c r="N833" s="44" t="s">
         <v>665</v>
       </c>
-      <c r="M833" s="37" t="s">
+      <c r="O833" s="44" t="s">
         <v>666</v>
       </c>
-      <c r="N833" s="44" t="s">
+      <c r="P833" s="44" t="s">
         <v>667</v>
-      </c>
-      <c r="O833" s="44" t="s">
-        <v>668</v>
-      </c>
-      <c r="P833" s="44" t="s">
-        <v>669</v>
       </c>
       <c r="Q833">
         <v>3</v>
@@ -39830,19 +39978,19 @@
         <v>1</v>
       </c>
       <c r="L834" s="28" t="s">
+        <v>663</v>
+      </c>
+      <c r="M834" s="37" t="s">
+        <v>664</v>
+      </c>
+      <c r="N834" s="44" t="s">
         <v>665</v>
       </c>
-      <c r="M834" s="37" t="s">
+      <c r="O834" s="44" t="s">
         <v>666</v>
       </c>
-      <c r="N834" s="44" t="s">
+      <c r="P834" s="44" t="s">
         <v>667</v>
-      </c>
-      <c r="O834" s="44" t="s">
-        <v>668</v>
-      </c>
-      <c r="P834" s="44" t="s">
-        <v>669</v>
       </c>
       <c r="Q834">
         <v>3</v>
@@ -39877,19 +40025,19 @@
         <v>1</v>
       </c>
       <c r="L835" s="28" t="s">
+        <v>663</v>
+      </c>
+      <c r="M835" s="37" t="s">
+        <v>664</v>
+      </c>
+      <c r="N835" s="44" t="s">
         <v>665</v>
       </c>
-      <c r="M835" s="37" t="s">
+      <c r="O835" s="44" t="s">
         <v>666</v>
       </c>
-      <c r="N835" s="44" t="s">
+      <c r="P835" s="44" t="s">
         <v>667</v>
-      </c>
-      <c r="O835" s="44" t="s">
-        <v>668</v>
-      </c>
-      <c r="P835" s="44" t="s">
-        <v>669</v>
       </c>
       <c r="Q835">
         <v>3</v>
@@ -39924,19 +40072,19 @@
         <v>1</v>
       </c>
       <c r="L836" s="28" t="s">
+        <v>663</v>
+      </c>
+      <c r="M836" s="37" t="s">
+        <v>664</v>
+      </c>
+      <c r="N836" s="44" t="s">
         <v>665</v>
       </c>
-      <c r="M836" s="37" t="s">
+      <c r="O836" s="44" t="s">
         <v>666</v>
       </c>
-      <c r="N836" s="44" t="s">
+      <c r="P836" s="44" t="s">
         <v>667</v>
-      </c>
-      <c r="O836" s="44" t="s">
-        <v>668</v>
-      </c>
-      <c r="P836" s="44" t="s">
-        <v>669</v>
       </c>
       <c r="Q836">
         <v>3</v>
@@ -39947,7 +40095,7 @@
     </row>
     <row r="837" spans="1:18" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A837" s="3" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="B837" s="28">
         <v>20000113</v>
@@ -39974,19 +40122,19 @@
         <v>1</v>
       </c>
       <c r="L837" s="46" t="s">
+        <v>674</v>
+      </c>
+      <c r="M837" s="46" t="s">
+        <v>675</v>
+      </c>
+      <c r="N837" s="46" t="s">
         <v>676</v>
       </c>
-      <c r="M837" s="46" t="s">
+      <c r="O837" s="46" t="s">
         <v>677</v>
       </c>
-      <c r="N837" s="46" t="s">
+      <c r="P837" s="47" t="s">
         <v>678</v>
-      </c>
-      <c r="O837" s="46" t="s">
-        <v>679</v>
-      </c>
-      <c r="P837" s="47" t="s">
-        <v>680</v>
       </c>
       <c r="Q837">
         <v>3</v>
@@ -40021,19 +40169,19 @@
         <v>1</v>
       </c>
       <c r="L838" s="46" t="s">
+        <v>674</v>
+      </c>
+      <c r="M838" s="46" t="s">
+        <v>675</v>
+      </c>
+      <c r="N838" s="46" t="s">
         <v>676</v>
       </c>
-      <c r="M838" s="46" t="s">
+      <c r="O838" s="46" t="s">
         <v>677</v>
       </c>
-      <c r="N838" s="46" t="s">
+      <c r="P838" s="47" t="s">
         <v>678</v>
-      </c>
-      <c r="O838" s="46" t="s">
-        <v>679</v>
-      </c>
-      <c r="P838" s="47" t="s">
-        <v>680</v>
       </c>
       <c r="Q838">
         <v>3</v>
@@ -40068,19 +40216,19 @@
         <v>1</v>
       </c>
       <c r="L839" s="46" t="s">
+        <v>674</v>
+      </c>
+      <c r="M839" s="46" t="s">
+        <v>675</v>
+      </c>
+      <c r="N839" s="46" t="s">
         <v>676</v>
       </c>
-      <c r="M839" s="46" t="s">
+      <c r="O839" s="46" t="s">
         <v>677</v>
       </c>
-      <c r="N839" s="46" t="s">
+      <c r="P839" s="47" t="s">
         <v>678</v>
-      </c>
-      <c r="O839" s="46" t="s">
-        <v>679</v>
-      </c>
-      <c r="P839" s="47" t="s">
-        <v>680</v>
       </c>
       <c r="Q839">
         <v>3</v>
@@ -40115,19 +40263,19 @@
         <v>1</v>
       </c>
       <c r="L840" s="46" t="s">
+        <v>674</v>
+      </c>
+      <c r="M840" s="46" t="s">
+        <v>675</v>
+      </c>
+      <c r="N840" s="46" t="s">
         <v>676</v>
       </c>
-      <c r="M840" s="46" t="s">
+      <c r="O840" s="46" t="s">
         <v>677</v>
       </c>
-      <c r="N840" s="46" t="s">
+      <c r="P840" s="47" t="s">
         <v>678</v>
-      </c>
-      <c r="O840" s="46" t="s">
-        <v>679</v>
-      </c>
-      <c r="P840" s="47" t="s">
-        <v>680</v>
       </c>
       <c r="Q840">
         <v>3</v>
@@ -40138,7 +40286,7 @@
     </row>
     <row r="841" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A841" s="3" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="B841" s="28">
         <v>200029</v>
@@ -40165,19 +40313,19 @@
         <v>1</v>
       </c>
       <c r="L841" s="25" t="s">
+        <v>691</v>
+      </c>
+      <c r="M841" s="37" t="s">
+        <v>692</v>
+      </c>
+      <c r="N841" s="48" t="s">
         <v>693</v>
       </c>
-      <c r="M841" s="37" t="s">
+      <c r="O841" s="48" t="s">
         <v>694</v>
       </c>
-      <c r="N841" s="48" t="s">
+      <c r="P841" s="48" t="s">
         <v>695</v>
-      </c>
-      <c r="O841" s="48" t="s">
-        <v>696</v>
-      </c>
-      <c r="P841" s="48" t="s">
-        <v>697</v>
       </c>
       <c r="Q841">
         <v>3</v>
@@ -40212,19 +40360,19 @@
         <v>1</v>
       </c>
       <c r="L842" s="25" t="s">
+        <v>691</v>
+      </c>
+      <c r="M842" s="37" t="s">
+        <v>692</v>
+      </c>
+      <c r="N842" s="48" t="s">
         <v>693</v>
       </c>
-      <c r="M842" s="37" t="s">
+      <c r="O842" s="48" t="s">
         <v>694</v>
       </c>
-      <c r="N842" s="48" t="s">
+      <c r="P842" s="48" t="s">
         <v>695</v>
-      </c>
-      <c r="O842" s="48" t="s">
-        <v>696</v>
-      </c>
-      <c r="P842" s="48" t="s">
-        <v>697</v>
       </c>
       <c r="Q842">
         <v>3</v>
@@ -40259,19 +40407,19 @@
         <v>1</v>
       </c>
       <c r="L843" s="25" t="s">
+        <v>691</v>
+      </c>
+      <c r="M843" s="37" t="s">
+        <v>692</v>
+      </c>
+      <c r="N843" s="48" t="s">
         <v>693</v>
       </c>
-      <c r="M843" s="37" t="s">
+      <c r="O843" s="48" t="s">
         <v>694</v>
       </c>
-      <c r="N843" s="48" t="s">
+      <c r="P843" s="48" t="s">
         <v>695</v>
-      </c>
-      <c r="O843" s="48" t="s">
-        <v>696</v>
-      </c>
-      <c r="P843" s="48" t="s">
-        <v>697</v>
       </c>
       <c r="Q843">
         <v>3</v>
@@ -40306,19 +40454,19 @@
         <v>1</v>
       </c>
       <c r="L844" s="25" t="s">
+        <v>691</v>
+      </c>
+      <c r="M844" s="37" t="s">
+        <v>692</v>
+      </c>
+      <c r="N844" s="48" t="s">
         <v>693</v>
       </c>
-      <c r="M844" s="37" t="s">
+      <c r="O844" s="48" t="s">
         <v>694</v>
       </c>
-      <c r="N844" s="48" t="s">
+      <c r="P844" s="48" t="s">
         <v>695</v>
-      </c>
-      <c r="O844" s="48" t="s">
-        <v>696</v>
-      </c>
-      <c r="P844" s="48" t="s">
-        <v>697</v>
       </c>
       <c r="Q844">
         <v>3</v>
@@ -40329,7 +40477,7 @@
     </row>
     <row r="845" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A845" s="3" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B845">
         <v>200005</v>
@@ -40355,20 +40503,20 @@
       <c r="I845">
         <v>1</v>
       </c>
-      <c r="L845" s="21" t="s">
-        <v>711</v>
-      </c>
-      <c r="M845" s="21" t="s">
-        <v>711</v>
-      </c>
-      <c r="N845" s="21" t="s">
-        <v>711</v>
-      </c>
-      <c r="O845" s="21" t="s">
-        <v>711</v>
-      </c>
-      <c r="P845" s="21" t="s">
-        <v>711</v>
+      <c r="L845" s="49" t="s">
+        <v>716</v>
+      </c>
+      <c r="M845" s="49" t="s">
+        <v>717</v>
+      </c>
+      <c r="N845" s="49" t="s">
+        <v>718</v>
+      </c>
+      <c r="O845" s="49" t="s">
+        <v>719</v>
+      </c>
+      <c r="P845" s="49" t="s">
+        <v>720</v>
       </c>
       <c r="Q845">
         <v>3</v>
@@ -40402,20 +40550,20 @@
       <c r="I846">
         <v>1</v>
       </c>
-      <c r="L846" s="21" t="s">
-        <v>711</v>
-      </c>
-      <c r="M846" s="21" t="s">
-        <v>711</v>
-      </c>
-      <c r="N846" s="21" t="s">
-        <v>711</v>
-      </c>
-      <c r="O846" s="21" t="s">
-        <v>711</v>
-      </c>
-      <c r="P846" s="21" t="s">
-        <v>711</v>
+      <c r="L846" s="49" t="s">
+        <v>721</v>
+      </c>
+      <c r="M846" s="49" t="s">
+        <v>722</v>
+      </c>
+      <c r="N846" s="49" t="s">
+        <v>723</v>
+      </c>
+      <c r="O846" s="49" t="s">
+        <v>724</v>
+      </c>
+      <c r="P846" s="49" t="s">
+        <v>725</v>
       </c>
       <c r="Q846">
         <v>3</v>
@@ -40449,20 +40597,20 @@
       <c r="I847">
         <v>1</v>
       </c>
-      <c r="L847" s="21" t="s">
-        <v>711</v>
-      </c>
-      <c r="M847" s="21" t="s">
-        <v>711</v>
-      </c>
-      <c r="N847" s="21" t="s">
-        <v>711</v>
-      </c>
-      <c r="O847" s="21" t="s">
-        <v>711</v>
-      </c>
-      <c r="P847" s="21" t="s">
-        <v>711</v>
+      <c r="L847" s="49" t="s">
+        <v>721</v>
+      </c>
+      <c r="M847" s="49" t="s">
+        <v>722</v>
+      </c>
+      <c r="N847" s="49" t="s">
+        <v>723</v>
+      </c>
+      <c r="O847" s="49" t="s">
+        <v>724</v>
+      </c>
+      <c r="P847" s="49" t="s">
+        <v>725</v>
       </c>
       <c r="Q847">
         <v>3</v>
@@ -40496,20 +40644,20 @@
       <c r="I848">
         <v>1</v>
       </c>
-      <c r="L848" s="21" t="s">
-        <v>711</v>
-      </c>
-      <c r="M848" s="21" t="s">
-        <v>711</v>
-      </c>
-      <c r="N848" s="21" t="s">
-        <v>711</v>
-      </c>
-      <c r="O848" s="21" t="s">
-        <v>711</v>
-      </c>
-      <c r="P848" s="21" t="s">
-        <v>711</v>
+      <c r="L848" s="49" t="s">
+        <v>721</v>
+      </c>
+      <c r="M848" s="49" t="s">
+        <v>722</v>
+      </c>
+      <c r="N848" s="49" t="s">
+        <v>723</v>
+      </c>
+      <c r="O848" s="49" t="s">
+        <v>724</v>
+      </c>
+      <c r="P848" s="49" t="s">
+        <v>725</v>
       </c>
       <c r="Q848">
         <v>3</v>
@@ -40518,7 +40666,7 @@
         <v>403207</v>
       </c>
     </row>
-    <row r="849" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="849" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B849">
         <v>200025</v>
       </c>
@@ -40543,20 +40691,20 @@
       <c r="I849">
         <v>1</v>
       </c>
-      <c r="L849" s="21" t="s">
-        <v>711</v>
-      </c>
-      <c r="M849" s="21" t="s">
-        <v>711</v>
-      </c>
-      <c r="N849" s="21" t="s">
-        <v>711</v>
-      </c>
-      <c r="O849" s="21" t="s">
-        <v>711</v>
-      </c>
-      <c r="P849" s="21" t="s">
-        <v>711</v>
+      <c r="L849" s="49" t="s">
+        <v>716</v>
+      </c>
+      <c r="M849" s="49" t="s">
+        <v>717</v>
+      </c>
+      <c r="N849" s="49" t="s">
+        <v>718</v>
+      </c>
+      <c r="O849" s="49" t="s">
+        <v>719</v>
+      </c>
+      <c r="P849" s="49" t="s">
+        <v>720</v>
       </c>
       <c r="Q849">
         <v>3</v>
@@ -40565,7 +40713,7 @@
         <v>402505</v>
       </c>
     </row>
-    <row r="850" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="850" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B850">
         <v>200039</v>
       </c>
@@ -40590,26 +40738,170 @@
       <c r="I850">
         <v>1</v>
       </c>
-      <c r="L850" s="21" t="s">
-        <v>711</v>
-      </c>
-      <c r="M850" s="21" t="s">
-        <v>711</v>
-      </c>
-      <c r="N850" s="21" t="s">
-        <v>711</v>
-      </c>
-      <c r="O850" s="21" t="s">
-        <v>711</v>
-      </c>
-      <c r="P850" s="21" t="s">
-        <v>711</v>
+      <c r="L850" s="49" t="s">
+        <v>721</v>
+      </c>
+      <c r="M850" s="49" t="s">
+        <v>722</v>
+      </c>
+      <c r="N850" s="49" t="s">
+        <v>723</v>
+      </c>
+      <c r="O850" s="49" t="s">
+        <v>724</v>
+      </c>
+      <c r="P850" s="49" t="s">
+        <v>725</v>
       </c>
       <c r="Q850">
         <v>3</v>
       </c>
       <c r="R850">
         <v>403905</v>
+      </c>
+    </row>
+    <row r="851" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A851" s="3" t="s">
+        <v>726</v>
+      </c>
+      <c r="B851">
+        <v>200099</v>
+      </c>
+      <c r="C851">
+        <v>931</v>
+      </c>
+      <c r="D851" t="s">
+        <v>102</v>
+      </c>
+      <c r="E851" t="s">
+        <v>103</v>
+      </c>
+      <c r="F851" t="s">
+        <v>104</v>
+      </c>
+      <c r="G851" t="s">
+        <v>105</v>
+      </c>
+      <c r="H851" t="s">
+        <v>106</v>
+      </c>
+      <c r="I851">
+        <v>1</v>
+      </c>
+      <c r="L851" s="37" t="s">
+        <v>727</v>
+      </c>
+      <c r="M851" s="27" t="s">
+        <v>728</v>
+      </c>
+      <c r="N851" s="27" t="s">
+        <v>729</v>
+      </c>
+      <c r="O851" s="27" t="s">
+        <v>730</v>
+      </c>
+      <c r="P851" s="27" t="s">
+        <v>731</v>
+      </c>
+      <c r="Q851">
+        <v>3</v>
+      </c>
+      <c r="R851">
+        <v>409903</v>
+      </c>
+    </row>
+    <row r="852" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="B852">
+        <v>200098</v>
+      </c>
+      <c r="C852">
+        <v>931</v>
+      </c>
+      <c r="D852" t="s">
+        <v>102</v>
+      </c>
+      <c r="E852" t="s">
+        <v>103</v>
+      </c>
+      <c r="F852" t="s">
+        <v>104</v>
+      </c>
+      <c r="G852" t="s">
+        <v>105</v>
+      </c>
+      <c r="H852" t="s">
+        <v>106</v>
+      </c>
+      <c r="I852">
+        <v>1</v>
+      </c>
+      <c r="L852" s="37" t="s">
+        <v>727</v>
+      </c>
+      <c r="M852" s="27" t="s">
+        <v>728</v>
+      </c>
+      <c r="N852" s="27" t="s">
+        <v>729</v>
+      </c>
+      <c r="O852" s="27" t="s">
+        <v>730</v>
+      </c>
+      <c r="P852" s="27" t="s">
+        <v>731</v>
+      </c>
+      <c r="Q852">
+        <v>3</v>
+      </c>
+      <c r="R852">
+        <v>409803</v>
+      </c>
+    </row>
+    <row r="853" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="B853">
+        <v>200097</v>
+      </c>
+      <c r="C853">
+        <v>931</v>
+      </c>
+      <c r="D853" t="s">
+        <v>102</v>
+      </c>
+      <c r="E853" t="s">
+        <v>103</v>
+      </c>
+      <c r="F853" t="s">
+        <v>104</v>
+      </c>
+      <c r="G853" t="s">
+        <v>105</v>
+      </c>
+      <c r="H853" t="s">
+        <v>106</v>
+      </c>
+      <c r="I853">
+        <v>1</v>
+      </c>
+      <c r="L853" s="37" t="s">
+        <v>727</v>
+      </c>
+      <c r="M853" s="27" t="s">
+        <v>728</v>
+      </c>
+      <c r="N853" s="27" t="s">
+        <v>729</v>
+      </c>
+      <c r="O853" s="27" t="s">
+        <v>730</v>
+      </c>
+      <c r="P853" s="27" t="s">
+        <v>731</v>
+      </c>
+      <c r="Q853">
+        <v>3</v>
+      </c>
+      <c r="R853">
+        <v>409703</v>
       </c>
     </row>
   </sheetData>
@@ -40663,7 +40955,7 @@
         <v>360</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
@@ -40712,7 +41004,7 @@
         <v>46</v>
       </c>
       <c r="N3" s="42" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="O3" s="43"/>
       <c r="P3" s="43"/>
@@ -40743,10 +41035,10 @@
         <v>1960</v>
       </c>
       <c r="N4" s="42" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="O4" s="42" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="P4" s="43"/>
     </row>
@@ -40779,10 +41071,10 @@
         <v>1</v>
       </c>
       <c r="O5" s="42" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P5" s="42" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
@@ -40897,7 +41189,7 @@
         <v>374</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>375</v>
@@ -40920,7 +41212,7 @@
         <v>409502</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>376</v>
@@ -40946,13 +41238,13 @@
         <v>40011201</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -40963,13 +41255,13 @@
         <v>40011202</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -40980,13 +41272,13 @@
         <v>40011203</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -41003,10 +41295,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:U40"/>
+  <dimension ref="A1:U45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.375" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="12.25" customWidth="1"/>
     <col min="3" max="3" width="12.5" customWidth="1"/>
     <col min="4" max="4" width="17.25" customWidth="1"/>
@@ -41045,10 +41337,10 @@
         <v>381</v>
       </c>
       <c r="H1" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>489</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>491</v>
       </c>
       <c r="J1" t="s">
         <v>382</v>
@@ -41063,7 +41355,7 @@
         <v>385</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="85.5" x14ac:dyDescent="0.2">
@@ -41086,22 +41378,22 @@
         <v>389</v>
       </c>
       <c r="H2" s="23" t="s">
+        <v>490</v>
+      </c>
+      <c r="I2" s="23" t="s">
+        <v>491</v>
+      </c>
+      <c r="K2" s="23" t="s">
         <v>492</v>
       </c>
-      <c r="I2" s="23" t="s">
+      <c r="L2" s="23" t="s">
         <v>493</v>
       </c>
-      <c r="K2" s="23" t="s">
+      <c r="M2" s="23" t="s">
         <v>494</v>
       </c>
-      <c r="L2" s="23" t="s">
-        <v>495</v>
-      </c>
-      <c r="M2" s="23" t="s">
-        <v>496</v>
-      </c>
       <c r="N2" s="23" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.2">
@@ -41150,7 +41442,7 @@
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B4">
         <v>400506</v>
@@ -41159,10 +41451,10 @@
         <v>3</v>
       </c>
       <c r="E4" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="F4" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>391</v>
@@ -41180,7 +41472,7 @@
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B5">
         <v>403206</v>
@@ -41189,10 +41481,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="E5" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>394</v>
@@ -41213,7 +41505,7 @@
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="B6">
         <v>402406</v>
@@ -41237,7 +41529,7 @@
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B7">
         <v>401906</v>
@@ -41261,7 +41553,7 @@
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B8">
         <v>403304</v>
@@ -41285,7 +41577,7 @@
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B9">
         <v>405905</v>
@@ -41316,7 +41608,7 @@
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B10">
         <v>409502</v>
@@ -41335,7 +41627,7 @@
         <v>424</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="N10" s="31">
         <v>1</v>
@@ -41343,7 +41635,7 @@
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B11">
         <v>403805</v>
@@ -41370,7 +41662,7 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B12">
         <v>400305</v>
@@ -41394,7 +41686,7 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B13">
         <v>404505</v>
@@ -41403,7 +41695,7 @@
         <v>2</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>436</v>
@@ -41421,7 +41713,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B14">
         <v>404805</v>
@@ -41430,10 +41722,10 @@
         <v>2</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>448</v>
+        <v>714</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>449</v>
+        <v>715</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>437</v>
@@ -41451,7 +41743,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B15">
         <v>401709</v>
@@ -41460,14 +41752,14 @@
         <v>1</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="I15" s="3"/>
       <c r="K15" s="3" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="N15" s="31">
         <v>1</v>
@@ -41475,7 +41767,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B16">
         <v>406804</v>
@@ -41484,14 +41776,14 @@
         <v>1</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="I16" s="3"/>
       <c r="K16" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="L16" s="3" t="s">
         <v>467</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>469</v>
       </c>
       <c r="N16" s="31">
         <v>1</v>
@@ -41499,7 +41791,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B17" s="3">
         <v>400306</v>
@@ -41508,14 +41800,14 @@
         <v>1</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="I17" s="3"/>
       <c r="K17" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="L17" s="3" t="s">
         <v>480</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>482</v>
       </c>
       <c r="N17" s="31">
         <v>1</v>
@@ -41523,7 +41815,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="B18" s="3">
         <v>406004</v>
@@ -41532,16 +41824,16 @@
         <v>1</v>
       </c>
       <c r="H18" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="K18" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>490</v>
-      </c>
-      <c r="K18" s="3" t="s">
+      <c r="L18" s="3" t="s">
         <v>481</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>483</v>
       </c>
       <c r="N18" s="31">
         <v>1</v>
@@ -41549,7 +41841,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B19" s="3">
         <v>402407</v>
@@ -41558,13 +41850,13 @@
         <v>1</v>
       </c>
       <c r="H19" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="L19" s="3" t="s">
         <v>510</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>511</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>512</v>
       </c>
       <c r="N19" s="31">
         <v>1</v>
@@ -41572,7 +41864,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" s="29" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="B20">
         <v>40010803</v>
@@ -41582,25 +41874,25 @@
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="G20" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="K20" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="H20" s="3" t="s">
+      <c r="L20" s="3" t="s">
         <v>516</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>517</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>518</v>
       </c>
       <c r="N20" s="31"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21" s="28" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B21">
         <v>40010903</v>
@@ -41609,25 +41901,25 @@
         <v>2</v>
       </c>
       <c r="E21" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="H21" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="K21" s="3" t="s">
         <v>520</v>
       </c>
-      <c r="H21" s="3" t="s">
+      <c r="L21" s="3" t="s">
         <v>521</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>522</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>523</v>
       </c>
       <c r="N21" s="31"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" s="28" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="B22">
         <v>40011003</v>
@@ -41636,25 +41928,25 @@
         <v>2</v>
       </c>
       <c r="E22" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="H22" s="3" t="s">
         <v>524</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="K22" s="3" t="s">
         <v>525</v>
       </c>
-      <c r="H22" s="3" t="s">
+      <c r="L22" s="3" t="s">
         <v>526</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>527</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>528</v>
       </c>
       <c r="N22" s="31"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23" s="28" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B23">
         <v>40011103</v>
@@ -41663,25 +41955,25 @@
         <v>2</v>
       </c>
       <c r="E23" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="H23" s="3" t="s">
         <v>529</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="K23" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="H23" s="3" t="s">
+      <c r="L23" s="3" t="s">
         <v>531</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>532</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>533</v>
       </c>
       <c r="N23" s="31"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24" s="32" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B24">
         <v>402106</v>
@@ -41690,18 +41982,18 @@
         <v>1</v>
       </c>
       <c r="H24" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="L24" s="3" t="s">
         <v>570</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>571</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25" s="32" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B25">
         <v>405906</v>
@@ -41710,18 +42002,18 @@
         <v>1</v>
       </c>
       <c r="H25" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="L25" s="3" t="s">
         <v>573</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>574</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26" s="28" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B26">
         <v>401907</v>
@@ -41730,18 +42022,18 @@
         <v>1</v>
       </c>
       <c r="H26" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="L26" s="3" t="s">
         <v>578</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>579</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27" s="32" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B27">
         <v>400107</v>
@@ -41750,18 +42042,18 @@
         <v>1</v>
       </c>
       <c r="H27" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="L27" s="3" t="s">
         <v>589</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>590</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28" s="32" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="B28">
         <v>400907</v>
@@ -41770,18 +42062,18 @@
         <v>1</v>
       </c>
       <c r="H28" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="L28" s="3" t="s">
         <v>592</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>593</v>
-      </c>
-      <c r="L28" s="3" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29" s="32" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B29">
         <v>40011202</v>
@@ -41790,27 +42082,27 @@
         <v>2</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="H29" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="L29" s="3" t="s">
         <v>601</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>602</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>603</v>
-      </c>
       <c r="M29" s="3" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30" s="32" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B30">
         <v>40011203</v>
@@ -41819,27 +42111,27 @@
         <v>3</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="H30" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="L30" s="3" t="s">
         <v>605</v>
       </c>
-      <c r="K30" s="3" t="s">
-        <v>606</v>
-      </c>
-      <c r="L30" s="3" t="s">
-        <v>607</v>
-      </c>
       <c r="M30" s="3" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B31">
         <v>406704</v>
@@ -41848,21 +42140,21 @@
         <v>1</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="H31" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="L31" s="3" t="s">
         <v>609</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>610</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B32">
         <v>402606</v>
@@ -41871,18 +42163,18 @@
         <v>1</v>
       </c>
       <c r="H32" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="L32" s="3" t="s">
         <v>613</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>614</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B33">
         <v>409003</v>
@@ -41891,18 +42183,18 @@
         <v>2</v>
       </c>
       <c r="H33" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="L33" s="3" t="s">
         <v>617</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>618</v>
-      </c>
-      <c r="L33" s="3" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B34">
         <v>400709</v>
@@ -41911,18 +42203,18 @@
         <v>2</v>
       </c>
       <c r="H34" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="K34" s="3" t="s">
         <v>653</v>
       </c>
-      <c r="K34" s="3" t="s">
-        <v>655</v>
-      </c>
       <c r="L34" s="3" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B35">
         <v>40010703</v>
@@ -41931,24 +42223,24 @@
         <v>2</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B36">
         <v>402907</v>
@@ -41957,18 +42249,18 @@
         <v>1</v>
       </c>
       <c r="H36" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="L36" s="3" t="s">
         <v>685</v>
-      </c>
-      <c r="K36" s="3" t="s">
-        <v>686</v>
-      </c>
-      <c r="L36" s="3" t="s">
-        <v>687</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B37">
         <v>407404</v>
@@ -41977,24 +42269,24 @@
         <v>2</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="H37" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="L37" s="3" t="s">
         <v>688</v>
-      </c>
-      <c r="K37" s="3" t="s">
-        <v>689</v>
-      </c>
-      <c r="L37" s="3" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B38">
         <v>400508</v>
@@ -42003,21 +42295,21 @@
         <v>1</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="H38" s="3" t="s">
+        <v>697</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>698</v>
+      </c>
+      <c r="L38" s="3" t="s">
         <v>699</v>
-      </c>
-      <c r="K38" s="3" t="s">
-        <v>700</v>
-      </c>
-      <c r="L38" s="3" t="s">
-        <v>701</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="B39">
         <v>404806</v>
@@ -42026,18 +42318,18 @@
         <v>1</v>
       </c>
       <c r="H39" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="L39" s="3" t="s">
         <v>703</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>704</v>
-      </c>
-      <c r="L39" s="3" t="s">
-        <v>705</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="B40">
         <v>408404</v>
@@ -42046,13 +42338,117 @@
         <v>1</v>
       </c>
       <c r="H40" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="L40" s="3" t="s">
         <v>707</v>
       </c>
-      <c r="K40" s="3" t="s">
-        <v>708</v>
-      </c>
-      <c r="L40" s="3" t="s">
-        <v>709</v>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A41" s="3" t="s">
+        <v>732</v>
+      </c>
+      <c r="B41">
+        <v>409903</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>735</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A42" s="3" t="s">
+        <v>737</v>
+      </c>
+      <c r="B42">
+        <v>409803</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>738</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>739</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A43" s="3" t="s">
+        <v>741</v>
+      </c>
+      <c r="B43">
+        <v>403807</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>745</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A44" s="3" t="s">
+        <v>742</v>
+      </c>
+      <c r="B44">
+        <v>408304</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>747</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>748</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A45" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="B45">
+        <v>409203</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>750</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>751</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>752</v>
       </c>
     </row>
   </sheetData>

--- a/source/bin/excel/character.xlsx
+++ b/source/bin/excel/character.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\liqi-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04709DAC-548C-42CE-A686-47E72468D0AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1F91453-82E5-49FB-A520-993C93DD2880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -114,7 +114,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7376" uniqueCount="780">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7410" uniqueCount="798">
   <si>
     <t>sheet</t>
   </si>
@@ -3026,14 +3026,6 @@
     <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
-    <t>sn_se_40012403/celebrate</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>lf_se_40012503/celebrate</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
     <t>tr_se_40012203/greeting</t>
     <phoneticPr fontId="16" type="noConversion"/>
   </si>
@@ -3042,14 +3034,6 @@
     <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
-    <t>sn_se_40012403/greeting</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>lf_se_40012503/greeting</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
     <t>tr_se_40012203/click</t>
     <phoneticPr fontId="16" type="noConversion"/>
   </si>
@@ -3058,11 +3042,90 @@
     <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
-    <t>sn_se_40012403/click</t>
+    <t>泽尼娅温泉</t>
     <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
-    <t>lf_se_40012503/click</t>
+    <t>zeniya_26wq_eff1</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>zeniya_26wq_eff3</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>zny_se_400908/celebrate</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>zny_se_400908/greeting</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>zny_se_400908/click</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>26wenquanx2</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>共沐夜色</t>
+  </si>
+  <si>
+    <t>素敵な夜と共に</t>
+  </si>
+  <si>
+    <t>Sipping the Night</t>
+  </si>
+  <si>
+    <t>같이 머무는 밤</t>
+  </si>
+  <si>
+    <t>lifa_1_eff_eff1</t>
+  </si>
+  <si>
+    <t>lifa_1_eff_eff2</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>shinai_1_eff_eff2</t>
+  </si>
+  <si>
+    <t>tongren_1_eff_eff2</t>
+  </si>
+  <si>
+    <t>tongren_1_eff_eff3</t>
+  </si>
+  <si>
+    <t>yasina_1_eff_eff1</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>yasina_1_eff_eff2</t>
+  </si>
+  <si>
+    <t>lf_se_40012403/celebrate</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>sn_se_40012503/celebrate</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>lf_se_40012403/greeting</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>sn_se_40012503/greeting</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>lf_se_40012403/click</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>sn_se_40012503/click</t>
     <phoneticPr fontId="16" type="noConversion"/>
   </si>
 </sst>
@@ -3951,7 +4014,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:U885"/>
+  <dimension ref="A1:U887"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
@@ -42051,10 +42114,10 @@
     </row>
     <row r="882" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A882" s="3" t="s">
-        <v>762</v>
-      </c>
-      <c r="B882" s="28">
-        <v>20000122</v>
+        <v>780</v>
+      </c>
+      <c r="B882">
+        <v>200009</v>
       </c>
       <c r="C882">
         <v>929</v>
@@ -42077,31 +42140,31 @@
       <c r="I882">
         <v>1</v>
       </c>
-      <c r="L882" s="25" t="s">
-        <v>763</v>
-      </c>
-      <c r="M882" s="25" t="s">
-        <v>763</v>
-      </c>
-      <c r="N882" s="25" t="s">
-        <v>763</v>
-      </c>
-      <c r="O882" s="25" t="s">
-        <v>763</v>
-      </c>
-      <c r="P882" s="25" t="s">
-        <v>763</v>
+      <c r="L882" s="27" t="s">
+        <v>781</v>
+      </c>
+      <c r="M882" s="27" t="s">
+        <v>781</v>
+      </c>
+      <c r="N882" s="27" t="s">
+        <v>782</v>
+      </c>
+      <c r="O882" s="29" t="s">
+        <v>783</v>
+      </c>
+      <c r="P882" s="27" t="s">
+        <v>784</v>
       </c>
       <c r="Q882">
         <v>3</v>
       </c>
       <c r="R882">
-        <v>40012203</v>
+        <v>400908</v>
       </c>
     </row>
     <row r="883" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="B883" s="28">
-        <v>20000123</v>
+      <c r="B883">
+        <v>200033</v>
       </c>
       <c r="C883">
         <v>929</v>
@@ -42124,34 +42187,37 @@
       <c r="I883">
         <v>1</v>
       </c>
-      <c r="L883" s="25" t="s">
-        <v>763</v>
-      </c>
-      <c r="M883" s="25" t="s">
-        <v>763</v>
-      </c>
-      <c r="N883" s="25" t="s">
-        <v>763</v>
-      </c>
-      <c r="O883" s="25" t="s">
-        <v>763</v>
-      </c>
-      <c r="P883" s="25" t="s">
-        <v>763</v>
+      <c r="L883" s="27" t="s">
+        <v>781</v>
+      </c>
+      <c r="M883" s="27" t="s">
+        <v>781</v>
+      </c>
+      <c r="N883" s="27" t="s">
+        <v>782</v>
+      </c>
+      <c r="O883" s="29" t="s">
+        <v>783</v>
+      </c>
+      <c r="P883" s="27" t="s">
+        <v>784</v>
       </c>
       <c r="Q883">
         <v>3</v>
       </c>
       <c r="R883">
-        <v>40012303</v>
+        <v>403305</v>
       </c>
     </row>
     <row r="884" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A884" s="3" t="s">
+        <v>762</v>
+      </c>
       <c r="B884" s="28">
-        <v>20000124</v>
+        <v>20000122</v>
       </c>
       <c r="C884">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D884" t="s">
         <v>102</v>
@@ -42190,15 +42256,15 @@
         <v>3</v>
       </c>
       <c r="R884">
-        <v>40012403</v>
+        <v>40012203</v>
       </c>
     </row>
     <row r="885" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B885" s="28">
-        <v>20000125</v>
+        <v>20000123</v>
       </c>
       <c r="C885">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D885" t="s">
         <v>102</v>
@@ -42237,6 +42303,100 @@
         <v>3</v>
       </c>
       <c r="R885">
+        <v>40012303</v>
+      </c>
+    </row>
+    <row r="886" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="B886" s="28">
+        <v>20000124</v>
+      </c>
+      <c r="C886">
+        <v>928</v>
+      </c>
+      <c r="D886" t="s">
+        <v>102</v>
+      </c>
+      <c r="E886" t="s">
+        <v>103</v>
+      </c>
+      <c r="F886" t="s">
+        <v>104</v>
+      </c>
+      <c r="G886" t="s">
+        <v>105</v>
+      </c>
+      <c r="H886" t="s">
+        <v>106</v>
+      </c>
+      <c r="I886">
+        <v>1</v>
+      </c>
+      <c r="L886" s="25" t="s">
+        <v>763</v>
+      </c>
+      <c r="M886" s="25" t="s">
+        <v>763</v>
+      </c>
+      <c r="N886" s="25" t="s">
+        <v>763</v>
+      </c>
+      <c r="O886" s="25" t="s">
+        <v>763</v>
+      </c>
+      <c r="P886" s="25" t="s">
+        <v>763</v>
+      </c>
+      <c r="Q886">
+        <v>3</v>
+      </c>
+      <c r="R886">
+        <v>40012403</v>
+      </c>
+    </row>
+    <row r="887" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="B887" s="28">
+        <v>20000125</v>
+      </c>
+      <c r="C887">
+        <v>928</v>
+      </c>
+      <c r="D887" t="s">
+        <v>102</v>
+      </c>
+      <c r="E887" t="s">
+        <v>103</v>
+      </c>
+      <c r="F887" t="s">
+        <v>104</v>
+      </c>
+      <c r="G887" t="s">
+        <v>105</v>
+      </c>
+      <c r="H887" t="s">
+        <v>106</v>
+      </c>
+      <c r="I887">
+        <v>1</v>
+      </c>
+      <c r="L887" s="25" t="s">
+        <v>763</v>
+      </c>
+      <c r="M887" s="25" t="s">
+        <v>763</v>
+      </c>
+      <c r="N887" s="25" t="s">
+        <v>763</v>
+      </c>
+      <c r="O887" s="25" t="s">
+        <v>763</v>
+      </c>
+      <c r="P887" s="25" t="s">
+        <v>763</v>
+      </c>
+      <c r="Q887">
+        <v>3</v>
+      </c>
+      <c r="R887">
         <v>40012503</v>
       </c>
     </row>
@@ -42631,7 +42791,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:U49"/>
+  <dimension ref="A1:U50"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -43798,62 +43958,81 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
-        <v>764</v>
+        <v>774</v>
       </c>
       <c r="B46">
-        <v>40012203</v>
+        <v>400908</v>
       </c>
       <c r="C46">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>775</v>
+      </c>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3" t="s">
+        <v>776</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>768</v>
+        <v>777</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>772</v>
+        <v>778</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B47">
-        <v>40012303</v>
+        <v>40012203</v>
       </c>
       <c r="C47">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="E47" t="s">
+        <v>788</v>
+      </c>
+      <c r="F47" t="s">
+        <v>789</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>777</v>
+        <v>772</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B48">
-        <v>40012403</v>
+        <v>40012303</v>
       </c>
       <c r="C48">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>790</v>
+      </c>
+      <c r="E48" t="s">
+        <v>791</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.2">
@@ -43861,19 +44040,48 @@
         <v>767</v>
       </c>
       <c r="B49">
+        <v>40012403</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+      <c r="D49" t="s">
+        <v>785</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>786</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>792</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>794</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A50" s="3" t="s">
+        <v>766</v>
+      </c>
+      <c r="B50">
         <v>40012503</v>
       </c>
-      <c r="C49">
-        <v>1</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>771</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>775</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>779</v>
+      <c r="C50">
+        <v>3</v>
+      </c>
+      <c r="E50" t="s">
+        <v>787</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>793</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>795</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>797</v>
       </c>
     </row>
   </sheetData>

--- a/source/bin/excel/character.xlsx
+++ b/source/bin/excel/character.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\liqi-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1F91453-82E5-49FB-A520-993C93DD2880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2790F18-5EF1-4112-8C20-8BC47E33920F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="export" sheetId="4" r:id="rId1"/>
@@ -114,7 +114,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7410" uniqueCount="798">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7410" uniqueCount="802">
   <si>
     <t>sheet</t>
   </si>
@@ -2998,10 +2998,6 @@
     <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
-    <t>tbd</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
     <t>桐人</t>
     <phoneticPr fontId="16" type="noConversion"/>
   </si>
@@ -3127,6 +3123,21 @@
   <si>
     <t>sn_se_40012503/click</t>
     <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>绀碧之界</t>
+  </si>
+  <si>
+    <t>紺碧之界</t>
+  </si>
+  <si>
+    <t>紺碧の境界</t>
+  </si>
+  <si>
+    <t>Azure Expanse</t>
+  </si>
+  <si>
+    <t>짙푸른 경계</t>
   </si>
 </sst>
 </file>
@@ -42114,7 +42125,7 @@
     </row>
     <row r="882" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A882" s="3" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B882">
         <v>200009</v>
@@ -42141,19 +42152,19 @@
         <v>1</v>
       </c>
       <c r="L882" s="27" t="s">
+        <v>780</v>
+      </c>
+      <c r="M882" s="27" t="s">
+        <v>780</v>
+      </c>
+      <c r="N882" s="27" t="s">
         <v>781</v>
       </c>
-      <c r="M882" s="27" t="s">
-        <v>781</v>
-      </c>
-      <c r="N882" s="27" t="s">
+      <c r="O882" s="29" t="s">
         <v>782</v>
       </c>
-      <c r="O882" s="29" t="s">
+      <c r="P882" s="27" t="s">
         <v>783</v>
-      </c>
-      <c r="P882" s="27" t="s">
-        <v>784</v>
       </c>
       <c r="Q882">
         <v>3</v>
@@ -42188,19 +42199,19 @@
         <v>1</v>
       </c>
       <c r="L883" s="27" t="s">
+        <v>780</v>
+      </c>
+      <c r="M883" s="27" t="s">
+        <v>780</v>
+      </c>
+      <c r="N883" s="27" t="s">
         <v>781</v>
       </c>
-      <c r="M883" s="27" t="s">
-        <v>781</v>
-      </c>
-      <c r="N883" s="27" t="s">
+      <c r="O883" s="29" t="s">
         <v>782</v>
       </c>
-      <c r="O883" s="29" t="s">
+      <c r="P883" s="27" t="s">
         <v>783</v>
-      </c>
-      <c r="P883" s="27" t="s">
-        <v>784</v>
       </c>
       <c r="Q883">
         <v>3</v>
@@ -42238,19 +42249,19 @@
         <v>1</v>
       </c>
       <c r="L884" s="25" t="s">
-        <v>763</v>
+        <v>797</v>
       </c>
       <c r="M884" s="25" t="s">
-        <v>763</v>
+        <v>798</v>
       </c>
       <c r="N884" s="25" t="s">
-        <v>763</v>
+        <v>799</v>
       </c>
       <c r="O884" s="25" t="s">
-        <v>763</v>
+        <v>800</v>
       </c>
       <c r="P884" s="25" t="s">
-        <v>763</v>
+        <v>801</v>
       </c>
       <c r="Q884">
         <v>3</v>
@@ -42285,19 +42296,19 @@
         <v>1</v>
       </c>
       <c r="L885" s="25" t="s">
-        <v>763</v>
+        <v>797</v>
       </c>
       <c r="M885" s="25" t="s">
-        <v>763</v>
+        <v>798</v>
       </c>
       <c r="N885" s="25" t="s">
-        <v>763</v>
+        <v>799</v>
       </c>
       <c r="O885" s="25" t="s">
-        <v>763</v>
+        <v>800</v>
       </c>
       <c r="P885" s="25" t="s">
-        <v>763</v>
+        <v>801</v>
       </c>
       <c r="Q885">
         <v>3</v>
@@ -42332,19 +42343,19 @@
         <v>1</v>
       </c>
       <c r="L886" s="25" t="s">
-        <v>763</v>
+        <v>797</v>
       </c>
       <c r="M886" s="25" t="s">
-        <v>763</v>
+        <v>798</v>
       </c>
       <c r="N886" s="25" t="s">
-        <v>763</v>
+        <v>799</v>
       </c>
       <c r="O886" s="25" t="s">
-        <v>763</v>
+        <v>800</v>
       </c>
       <c r="P886" s="25" t="s">
-        <v>763</v>
+        <v>801</v>
       </c>
       <c r="Q886">
         <v>3</v>
@@ -42379,19 +42390,19 @@
         <v>1</v>
       </c>
       <c r="L887" s="25" t="s">
-        <v>763</v>
+        <v>797</v>
       </c>
       <c r="M887" s="25" t="s">
-        <v>763</v>
+        <v>798</v>
       </c>
       <c r="N887" s="25" t="s">
-        <v>763</v>
+        <v>799</v>
       </c>
       <c r="O887" s="25" t="s">
-        <v>763</v>
+        <v>800</v>
       </c>
       <c r="P887" s="25" t="s">
-        <v>763</v>
+        <v>801</v>
       </c>
       <c r="Q887">
         <v>3</v>
@@ -43958,7 +43969,7 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B46">
         <v>400908</v>
@@ -43967,25 +43978,25 @@
         <v>2</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="3" t="s">
+        <v>775</v>
+      </c>
+      <c r="H46" s="3" t="s">
         <v>776</v>
       </c>
-      <c r="H46" s="3" t="s">
+      <c r="K46" s="3" t="s">
         <v>777</v>
       </c>
-      <c r="K46" s="3" t="s">
+      <c r="L46" s="3" t="s">
         <v>778</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>779</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B47">
         <v>40012203</v>
@@ -43994,24 +44005,24 @@
         <v>3</v>
       </c>
       <c r="E47" t="s">
+        <v>787</v>
+      </c>
+      <c r="F47" t="s">
         <v>788</v>
       </c>
-      <c r="F47" t="s">
-        <v>789</v>
-      </c>
       <c r="H47" s="3" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B48">
         <v>40012303</v>
@@ -44020,24 +44031,24 @@
         <v>2</v>
       </c>
       <c r="D48" s="3" t="s">
+        <v>789</v>
+      </c>
+      <c r="E48" t="s">
         <v>790</v>
       </c>
-      <c r="E48" t="s">
-        <v>791</v>
-      </c>
       <c r="H48" s="3" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B49">
         <v>40012403</v>
@@ -44046,24 +44057,24 @@
         <v>1</v>
       </c>
       <c r="D49" t="s">
+        <v>784</v>
+      </c>
+      <c r="E49" s="3" t="s">
         <v>785</v>
       </c>
-      <c r="E49" s="3" t="s">
-        <v>786</v>
-      </c>
       <c r="H49" s="3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B50">
         <v>40012503</v>
@@ -44072,16 +44083,16 @@
         <v>3</v>
       </c>
       <c r="E50" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
   </sheetData>

--- a/source/bin/excel/character.xlsx
+++ b/source/bin/excel/character.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VIP\Desktop\检查5+6月手合表\6月主配置\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\liqi-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{345994A9-A59E-4DFB-A3C0-8049137BD4DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E63F8A68-F9F8-444D-8C87-D78B2A596040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14895" yWindow="0" windowWidth="13905" windowHeight="16200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="export" sheetId="4" r:id="rId1"/>
@@ -114,7 +114,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7434" uniqueCount="774">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7519" uniqueCount="869">
   <si>
     <t>sheet</t>
   </si>
@@ -2853,10 +2853,6 @@
     <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
-    <t>tbd</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
     <t>桐人</t>
     <phoneticPr fontId="16" type="noConversion"/>
   </si>
@@ -3028,16 +3024,311 @@
     <t>짙푸른 경계</t>
   </si>
   <si>
-    <t>为你应援！</t>
-  </si>
-  <si>
-    <t>為你應援！</t>
-  </si>
-  <si>
-    <t>Go! Sparkle! Shine!</t>
-  </si>
-  <si>
-    <t>너를 향한 응원!</t>
+    <t>26hxsw3</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>弥拉_幻想生物</t>
+  </si>
+  <si>
+    <t>ml_se_40011703/celebrate</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>ml_se_40011703/greeting</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>ml_se_40011703/click</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>七海礼奈_幻想生物</t>
+  </si>
+  <si>
+    <t>qhln_se_404406/celebrate</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>qhln_se_404406/greeting</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>qhln_se_404406/click</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>凉宫杏树浴衣</t>
+  </si>
+  <si>
+    <t>LGXS_SE_402104/celebrate</t>
+  </si>
+  <si>
+    <t>LGXS_SE_402104/greeting</t>
+  </si>
+  <si>
+    <t>LGXS_SE_402104/click</t>
+  </si>
+  <si>
+    <t>A-37浴衣</t>
+  </si>
+  <si>
+    <t>A37_SE_404503/celebrate</t>
+  </si>
+  <si>
+    <t>A37_SE_404503/greeting</t>
+  </si>
+  <si>
+    <t>A37_SE_404503/click</t>
+  </si>
+  <si>
+    <t>西园寺一羽契约</t>
+  </si>
+  <si>
+    <t>XYSYY_SE_405202/celebrate</t>
+  </si>
+  <si>
+    <t>XYSYY_SE_405202/greeting</t>
+  </si>
+  <si>
+    <t>XYSYY_SE_405202/click</t>
+  </si>
+  <si>
+    <t>XYSYY_SE_405202/click2</t>
+  </si>
+  <si>
+    <t>辉夜姬春节</t>
+  </si>
+  <si>
+    <t>HYJ_SE_402904/celebrate</t>
+  </si>
+  <si>
+    <t>HYJ_SE_402904/greeting</t>
+  </si>
+  <si>
+    <t>HYJ_SE_402904/click</t>
+  </si>
+  <si>
+    <t>艾丽莎春节</t>
+  </si>
+  <si>
+    <t>ALS_SE_403204/celebrate</t>
+  </si>
+  <si>
+    <t>ALS_SE_403204/greeting</t>
+  </si>
+  <si>
+    <t>ALS_SE_403204/click</t>
+  </si>
+  <si>
+    <t>森川绫子睡衣</t>
+  </si>
+  <si>
+    <t>SCLZ_SE_404803/celebrate</t>
+  </si>
+  <si>
+    <t>SCLZ_SE_404803/greeting</t>
+  </si>
+  <si>
+    <t>SCLZ_SE_404803/click</t>
+  </si>
+  <si>
+    <t>八木唯夏日</t>
+  </si>
+  <si>
+    <t>BMW_SE_400706/celebrate</t>
+  </si>
+  <si>
+    <t>BMW_SE_400706/greeting</t>
+  </si>
+  <si>
+    <t>BMW_SE_400706/click</t>
+  </si>
+  <si>
+    <t>四宫夏生夏日</t>
+  </si>
+  <si>
+    <t>SGXS_SE_401105/celebrate</t>
+  </si>
+  <si>
+    <t>SGXS_SE_401105/greeting</t>
+  </si>
+  <si>
+    <t>SGXS_SE_401105/click</t>
+  </si>
+  <si>
+    <t>北原莉莉契约</t>
+  </si>
+  <si>
+    <t>BYLL_SE_406102/celebrate</t>
+  </si>
+  <si>
+    <t>BYLL_SE_406102/greeting</t>
+  </si>
+  <si>
+    <t>BYLL_SE_406102/click</t>
+  </si>
+  <si>
+    <t>BYLL_SE_406102/click2</t>
+  </si>
+  <si>
+    <t>相原舞万圣</t>
+  </si>
+  <si>
+    <t>XYW_SE_400505/celebrate</t>
+  </si>
+  <si>
+    <t>XYW_SE_400505/greeting</t>
+  </si>
+  <si>
+    <t>XYW_SE_400505/click</t>
+  </si>
+  <si>
+    <t>月见山万圣</t>
+  </si>
+  <si>
+    <t>YJS_SE_402704/celebrate</t>
+  </si>
+  <si>
+    <t>YJS_SE_402704/greeting</t>
+  </si>
+  <si>
+    <t>YJS_SE_402704/click</t>
+  </si>
+  <si>
+    <t>五十岚阳菜元旦</t>
+  </si>
+  <si>
+    <t>WSLYC_SE_402005/celebrate</t>
+  </si>
+  <si>
+    <t>WSLYC_SE_402005/greeting</t>
+  </si>
+  <si>
+    <t>WSLYC_SE_402005/click</t>
+  </si>
+  <si>
+    <t>姬川响元旦</t>
+  </si>
+  <si>
+    <t>JCX_SE_404603/celebrate</t>
+  </si>
+  <si>
+    <t>JCX_SE_404603/greeting</t>
+  </si>
+  <si>
+    <t>JCX_SE_404603/click</t>
+  </si>
+  <si>
+    <t>泽尼娅春节</t>
+  </si>
+  <si>
+    <t>ZNY_SE_400905/celebrate</t>
+  </si>
+  <si>
+    <t>ZNY_SE_400905/greeting</t>
+  </si>
+  <si>
+    <t>ZNY_SE_400905/click</t>
+  </si>
+  <si>
+    <t>一之濑空春节</t>
+  </si>
+  <si>
+    <t>YZLK_SE_401305/celebrate</t>
+  </si>
+  <si>
+    <t>YZLK_SE_401305/greeting</t>
+  </si>
+  <si>
+    <t>YZLK_SE_401305/click</t>
+  </si>
+  <si>
+    <t>卡维礼服</t>
+  </si>
+  <si>
+    <t>KW_SE_401004/celebrate</t>
+  </si>
+  <si>
+    <t>KW_SE_401004/greeting</t>
+  </si>
+  <si>
+    <t>KW_SE_401004/click</t>
+  </si>
+  <si>
+    <t>三上千织万圣</t>
+  </si>
+  <si>
+    <t>SSQZ_SE_400406/celebrate</t>
+  </si>
+  <si>
+    <t>SSQZ_SE_400406/greeting</t>
+  </si>
+  <si>
+    <t>SSQZ_SE_400406/click</t>
+  </si>
+  <si>
+    <t>莱恩万圣</t>
+  </si>
+  <si>
+    <t>LN_SE_404704/celebrate</t>
+  </si>
+  <si>
+    <t>LN_SE_404704/greeting</t>
+  </si>
+  <si>
+    <t>LN_SE_404704/click</t>
+  </si>
+  <si>
+    <t>如月莲元旦</t>
+  </si>
+  <si>
+    <t>RYL_SE_403004/celebrate</t>
+  </si>
+  <si>
+    <t>RYL_SE_403004/greeting</t>
+  </si>
+  <si>
+    <t>RYL_SE_403004/click</t>
+  </si>
+  <si>
+    <t>如月彩音圣诞</t>
+  </si>
+  <si>
+    <t>RYCY_SE_406803/celebrate</t>
+  </si>
+  <si>
+    <t>RYCY_SE_406803/greeting</t>
+  </si>
+  <si>
+    <t>RYCY_SE_406803/click</t>
+  </si>
+  <si>
+    <t>东城玄音契约</t>
+  </si>
+  <si>
+    <t>DCXY_SE_407602/celebrate</t>
+  </si>
+  <si>
+    <t>DCXY_SE_407602/greeting</t>
+  </si>
+  <si>
+    <t>DCXY_SE_407602/click</t>
+  </si>
+  <si>
+    <t>DCXY_SE_407602/click2</t>
+  </si>
+  <si>
+    <t>青鸾春节</t>
+  </si>
+  <si>
+    <t>QL_SE_406703/celebrate</t>
+  </si>
+  <si>
+    <t>QL_SE_406703/greeting</t>
+  </si>
+  <si>
+    <t>QL_SE_406703/click</t>
   </si>
 </sst>
 </file>
@@ -3323,7 +3614,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3375,6 +3666,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3435,7 +3732,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3559,12 +3856,23 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="표준 4" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3952,7 +4260,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:U893"/>
+  <dimension ref="A1:U896"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
@@ -42052,7 +42360,7 @@
     </row>
     <row r="882" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A882" s="3" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B882">
         <v>200009</v>
@@ -42079,19 +42387,19 @@
         <v>1</v>
       </c>
       <c r="L882" s="26" t="s">
+        <v>738</v>
+      </c>
+      <c r="M882" s="26" t="s">
+        <v>738</v>
+      </c>
+      <c r="N882" s="26" t="s">
         <v>739</v>
       </c>
-      <c r="M882" s="26" t="s">
-        <v>739</v>
-      </c>
-      <c r="N882" s="26" t="s">
+      <c r="O882" s="28" t="s">
         <v>740</v>
       </c>
-      <c r="O882" s="28" t="s">
+      <c r="P882" s="26" t="s">
         <v>741</v>
-      </c>
-      <c r="P882" s="26" t="s">
-        <v>742</v>
       </c>
       <c r="Q882">
         <v>3</v>
@@ -42126,19 +42434,19 @@
         <v>1</v>
       </c>
       <c r="L883" s="26" t="s">
+        <v>738</v>
+      </c>
+      <c r="M883" s="26" t="s">
+        <v>738</v>
+      </c>
+      <c r="N883" s="26" t="s">
         <v>739</v>
       </c>
-      <c r="M883" s="26" t="s">
-        <v>739</v>
-      </c>
-      <c r="N883" s="26" t="s">
+      <c r="O883" s="28" t="s">
         <v>740</v>
       </c>
-      <c r="O883" s="28" t="s">
+      <c r="P883" s="26" t="s">
         <v>741</v>
-      </c>
-      <c r="P883" s="26" t="s">
-        <v>742</v>
       </c>
       <c r="Q883">
         <v>3</v>
@@ -42176,19 +42484,19 @@
         <v>1</v>
       </c>
       <c r="L884" s="24" t="s">
+        <v>764</v>
+      </c>
+      <c r="M884" s="24" t="s">
         <v>765</v>
       </c>
-      <c r="M884" s="24" t="s">
+      <c r="N884" s="24" t="s">
         <v>766</v>
       </c>
-      <c r="N884" s="24" t="s">
+      <c r="O884" s="24" t="s">
         <v>767</v>
       </c>
-      <c r="O884" s="24" t="s">
+      <c r="P884" s="24" t="s">
         <v>768</v>
-      </c>
-      <c r="P884" s="24" t="s">
-        <v>769</v>
       </c>
       <c r="Q884">
         <v>3</v>
@@ -42223,19 +42531,19 @@
         <v>1</v>
       </c>
       <c r="L885" s="24" t="s">
+        <v>764</v>
+      </c>
+      <c r="M885" s="24" t="s">
         <v>765</v>
       </c>
-      <c r="M885" s="24" t="s">
+      <c r="N885" s="24" t="s">
         <v>766</v>
       </c>
-      <c r="N885" s="24" t="s">
+      <c r="O885" s="24" t="s">
         <v>767</v>
       </c>
-      <c r="O885" s="24" t="s">
+      <c r="P885" s="24" t="s">
         <v>768</v>
-      </c>
-      <c r="P885" s="24" t="s">
-        <v>769</v>
       </c>
       <c r="Q885">
         <v>3</v>
@@ -42270,19 +42578,19 @@
         <v>1</v>
       </c>
       <c r="L886" s="24" t="s">
+        <v>764</v>
+      </c>
+      <c r="M886" s="24" t="s">
         <v>765</v>
       </c>
-      <c r="M886" s="24" t="s">
+      <c r="N886" s="24" t="s">
         <v>766</v>
       </c>
-      <c r="N886" s="24" t="s">
+      <c r="O886" s="24" t="s">
         <v>767</v>
       </c>
-      <c r="O886" s="24" t="s">
+      <c r="P886" s="24" t="s">
         <v>768</v>
-      </c>
-      <c r="P886" s="24" t="s">
-        <v>769</v>
       </c>
       <c r="Q886">
         <v>3</v>
@@ -42317,19 +42625,19 @@
         <v>1</v>
       </c>
       <c r="L887" s="24" t="s">
+        <v>764</v>
+      </c>
+      <c r="M887" s="24" t="s">
         <v>765</v>
       </c>
-      <c r="M887" s="24" t="s">
+      <c r="N887" s="24" t="s">
         <v>766</v>
       </c>
-      <c r="N887" s="24" t="s">
+      <c r="O887" s="24" t="s">
         <v>767</v>
       </c>
-      <c r="O887" s="24" t="s">
+      <c r="P887" s="24" t="s">
         <v>768</v>
-      </c>
-      <c r="P887" s="24" t="s">
-        <v>769</v>
       </c>
       <c r="Q887">
         <v>3</v>
@@ -42340,7 +42648,7 @@
     </row>
     <row r="888" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A888" s="3" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B888">
         <v>200018</v>
@@ -42365,21 +42673,6 @@
       </c>
       <c r="I888">
         <v>1</v>
-      </c>
-      <c r="L888" s="26" t="s">
-        <v>770</v>
-      </c>
-      <c r="M888" s="26" t="s">
-        <v>771</v>
-      </c>
-      <c r="N888" s="24" t="s">
-        <v>723</v>
-      </c>
-      <c r="O888" s="26" t="s">
-        <v>772</v>
-      </c>
-      <c r="P888" s="26" t="s">
-        <v>773</v>
       </c>
       <c r="Q888">
         <v>3</v>
@@ -42413,21 +42706,6 @@
       <c r="I889">
         <v>1</v>
       </c>
-      <c r="L889" s="26" t="s">
-        <v>770</v>
-      </c>
-      <c r="M889" s="26" t="s">
-        <v>771</v>
-      </c>
-      <c r="N889" s="24" t="s">
-        <v>723</v>
-      </c>
-      <c r="O889" s="26" t="s">
-        <v>772</v>
-      </c>
-      <c r="P889" s="26" t="s">
-        <v>773</v>
-      </c>
       <c r="Q889">
         <v>3</v>
       </c>
@@ -42460,21 +42738,6 @@
       <c r="I890">
         <v>1</v>
       </c>
-      <c r="L890" s="26" t="s">
-        <v>770</v>
-      </c>
-      <c r="M890" s="26" t="s">
-        <v>771</v>
-      </c>
-      <c r="N890" s="24" t="s">
-        <v>723</v>
-      </c>
-      <c r="O890" s="26" t="s">
-        <v>772</v>
-      </c>
-      <c r="P890" s="26" t="s">
-        <v>773</v>
-      </c>
       <c r="Q890">
         <v>3</v>
       </c>
@@ -42507,21 +42770,6 @@
       <c r="I891">
         <v>1</v>
       </c>
-      <c r="L891" s="26" t="s">
-        <v>770</v>
-      </c>
-      <c r="M891" s="26" t="s">
-        <v>771</v>
-      </c>
-      <c r="N891" s="24" t="s">
-        <v>723</v>
-      </c>
-      <c r="O891" s="26" t="s">
-        <v>772</v>
-      </c>
-      <c r="P891" s="26" t="s">
-        <v>773</v>
-      </c>
       <c r="Q891">
         <v>3</v>
       </c>
@@ -42531,7 +42779,7 @@
     </row>
     <row r="892" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A892" s="3" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B892">
         <v>200050</v>
@@ -42556,21 +42804,6 @@
       </c>
       <c r="I892">
         <v>1</v>
-      </c>
-      <c r="L892" s="24" t="s">
-        <v>723</v>
-      </c>
-      <c r="M892" s="24" t="s">
-        <v>723</v>
-      </c>
-      <c r="N892" s="24" t="s">
-        <v>723</v>
-      </c>
-      <c r="O892" s="24" t="s">
-        <v>723</v>
-      </c>
-      <c r="P892" s="24" t="s">
-        <v>723</v>
       </c>
       <c r="Q892">
         <v>3</v>
@@ -42604,26 +42837,110 @@
       <c r="I893">
         <v>1</v>
       </c>
-      <c r="L893" s="24" t="s">
-        <v>723</v>
-      </c>
-      <c r="M893" s="24" t="s">
-        <v>723</v>
-      </c>
-      <c r="N893" s="24" t="s">
-        <v>723</v>
-      </c>
-      <c r="O893" s="24" t="s">
-        <v>723</v>
-      </c>
-      <c r="P893" s="24" t="s">
-        <v>723</v>
-      </c>
       <c r="Q893">
         <v>3</v>
       </c>
       <c r="R893">
         <v>405104</v>
+      </c>
+    </row>
+    <row r="894" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A894" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="B894">
+        <v>20000117</v>
+      </c>
+      <c r="C894">
+        <v>925</v>
+      </c>
+      <c r="D894" t="s">
+        <v>102</v>
+      </c>
+      <c r="E894" t="s">
+        <v>103</v>
+      </c>
+      <c r="F894" t="s">
+        <v>104</v>
+      </c>
+      <c r="G894" t="s">
+        <v>105</v>
+      </c>
+      <c r="H894" t="s">
+        <v>106</v>
+      </c>
+      <c r="I894">
+        <v>1</v>
+      </c>
+      <c r="Q894">
+        <v>3</v>
+      </c>
+      <c r="R894">
+        <v>40011703</v>
+      </c>
+    </row>
+    <row r="895" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="B895">
+        <v>200044</v>
+      </c>
+      <c r="C895">
+        <v>925</v>
+      </c>
+      <c r="D895" t="s">
+        <v>102</v>
+      </c>
+      <c r="E895" t="s">
+        <v>103</v>
+      </c>
+      <c r="F895" t="s">
+        <v>104</v>
+      </c>
+      <c r="G895" t="s">
+        <v>105</v>
+      </c>
+      <c r="H895" t="s">
+        <v>106</v>
+      </c>
+      <c r="I895">
+        <v>1</v>
+      </c>
+      <c r="Q895">
+        <v>3</v>
+      </c>
+      <c r="R895">
+        <v>404406</v>
+      </c>
+    </row>
+    <row r="896" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="B896">
+        <v>200031</v>
+      </c>
+      <c r="C896">
+        <v>925</v>
+      </c>
+      <c r="D896" t="s">
+        <v>102</v>
+      </c>
+      <c r="E896" t="s">
+        <v>103</v>
+      </c>
+      <c r="F896" t="s">
+        <v>104</v>
+      </c>
+      <c r="G896" t="s">
+        <v>105</v>
+      </c>
+      <c r="H896" t="s">
+        <v>106</v>
+      </c>
+      <c r="I896">
+        <v>1</v>
+      </c>
+      <c r="Q896">
+        <v>3</v>
+      </c>
+      <c r="R896">
+        <v>403105</v>
       </c>
     </row>
   </sheetData>
@@ -43009,7 +43326,7 @@
   </sheetData>
   <phoneticPr fontId="16" type="noConversion"/>
   <conditionalFormatting sqref="B12:B14">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -43017,7 +43334,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:R53"/>
+  <dimension ref="A1:R77"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -43043,7 +43360,7 @@
         <v>376</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>469</v>
@@ -43078,7 +43395,7 @@
         <v>381</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E2" s="22" t="s">
         <v>472</v>
@@ -44112,7 +44429,7 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B46">
         <v>400908</v>
@@ -44124,18 +44441,18 @@
         <v>1</v>
       </c>
       <c r="E46" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="H46" s="3" t="s">
         <v>735</v>
       </c>
-      <c r="H46" s="3" t="s">
+      <c r="I46" s="3" t="s">
         <v>736</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>737</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B47">
         <v>40012203</v>
@@ -44147,18 +44464,18 @@
         <v>1</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B48">
         <v>40012303</v>
@@ -44170,18 +44487,18 @@
         <v>1</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B49">
         <v>40012403</v>
@@ -44193,18 +44510,18 @@
         <v>1</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B50">
         <v>40012503</v>
@@ -44216,18 +44533,18 @@
         <v>1</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B51">
         <v>401806</v>
@@ -44236,18 +44553,18 @@
         <v>1</v>
       </c>
       <c r="E51" s="3" t="s">
+        <v>750</v>
+      </c>
+      <c r="H51" s="3" t="s">
         <v>751</v>
       </c>
-      <c r="H51" s="3" t="s">
+      <c r="I51" s="3" t="s">
         <v>752</v>
       </c>
-      <c r="I51" s="3" t="s">
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A52" s="3" t="s">
         <v>753</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A52" s="3" t="s">
-        <v>754</v>
       </c>
       <c r="B52" s="49">
         <v>405004</v>
@@ -44259,18 +44576,18 @@
         <v>1</v>
       </c>
       <c r="E52" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="H52" s="3" t="s">
         <v>756</v>
       </c>
-      <c r="H52" s="3" t="s">
+      <c r="I52" s="3" t="s">
         <v>757</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B53" s="49">
         <v>405104</v>
@@ -44282,21 +44599,539 @@
         <v>1</v>
       </c>
       <c r="E53" s="3" t="s">
+        <v>758</v>
+      </c>
+      <c r="H53" s="3" t="s">
         <v>759</v>
       </c>
-      <c r="H53" s="3" t="s">
+      <c r="I53" s="3" t="s">
         <v>760</v>
       </c>
-      <c r="I53" s="3" t="s">
-        <v>761</v>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A54" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="B54" s="49">
+        <v>40011703</v>
+      </c>
+      <c r="C54" s="51">
+        <v>1</v>
+      </c>
+      <c r="D54" s="50"/>
+      <c r="E54" s="3" t="s">
+        <v>771</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>772</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A55" s="3" t="s">
+        <v>774</v>
+      </c>
+      <c r="B55" s="49">
+        <v>404406</v>
+      </c>
+      <c r="C55" s="51">
+        <v>1</v>
+      </c>
+      <c r="D55" s="50">
+        <v>1</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>775</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>776</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>778</v>
+      </c>
+      <c r="B56">
+        <v>402104</v>
+      </c>
+      <c r="C56" s="51">
+        <v>1</v>
+      </c>
+      <c r="D56" s="51"/>
+      <c r="E56" t="s">
+        <v>779</v>
+      </c>
+      <c r="H56" t="s">
+        <v>780</v>
+      </c>
+      <c r="I56" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>782</v>
+      </c>
+      <c r="B57">
+        <v>404503</v>
+      </c>
+      <c r="C57" s="51">
+        <v>1</v>
+      </c>
+      <c r="D57" s="51"/>
+      <c r="E57" t="s">
+        <v>783</v>
+      </c>
+      <c r="H57" t="s">
+        <v>784</v>
+      </c>
+      <c r="I57" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>786</v>
+      </c>
+      <c r="B58">
+        <v>405202</v>
+      </c>
+      <c r="C58" s="51">
+        <v>1</v>
+      </c>
+      <c r="D58" s="51"/>
+      <c r="E58" t="s">
+        <v>787</v>
+      </c>
+      <c r="H58" t="s">
+        <v>788</v>
+      </c>
+      <c r="I58" t="s">
+        <v>789</v>
+      </c>
+      <c r="J58" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>791</v>
+      </c>
+      <c r="B59">
+        <v>402904</v>
+      </c>
+      <c r="C59" s="51">
+        <v>1</v>
+      </c>
+      <c r="D59" s="51"/>
+      <c r="E59" t="s">
+        <v>792</v>
+      </c>
+      <c r="H59" t="s">
+        <v>793</v>
+      </c>
+      <c r="I59" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>795</v>
+      </c>
+      <c r="B60">
+        <v>403204</v>
+      </c>
+      <c r="C60" s="51">
+        <v>1</v>
+      </c>
+      <c r="D60" s="51"/>
+      <c r="E60" t="s">
+        <v>796</v>
+      </c>
+      <c r="H60" t="s">
+        <v>797</v>
+      </c>
+      <c r="I60" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>799</v>
+      </c>
+      <c r="B61">
+        <v>404803</v>
+      </c>
+      <c r="C61" s="51">
+        <v>1</v>
+      </c>
+      <c r="D61" s="51"/>
+      <c r="E61" t="s">
+        <v>800</v>
+      </c>
+      <c r="H61" t="s">
+        <v>801</v>
+      </c>
+      <c r="I61" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>803</v>
+      </c>
+      <c r="B62">
+        <v>400706</v>
+      </c>
+      <c r="C62" s="51">
+        <v>1</v>
+      </c>
+      <c r="D62" s="51"/>
+      <c r="E62" t="s">
+        <v>804</v>
+      </c>
+      <c r="H62" t="s">
+        <v>805</v>
+      </c>
+      <c r="I62" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>807</v>
+      </c>
+      <c r="B63">
+        <v>401105</v>
+      </c>
+      <c r="C63" s="51">
+        <v>1</v>
+      </c>
+      <c r="D63" s="51"/>
+      <c r="E63" t="s">
+        <v>808</v>
+      </c>
+      <c r="H63" t="s">
+        <v>809</v>
+      </c>
+      <c r="I63" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>811</v>
+      </c>
+      <c r="B64">
+        <v>406102</v>
+      </c>
+      <c r="C64" s="51">
+        <v>1</v>
+      </c>
+      <c r="D64" s="51"/>
+      <c r="E64" t="s">
+        <v>812</v>
+      </c>
+      <c r="H64" t="s">
+        <v>813</v>
+      </c>
+      <c r="I64" t="s">
+        <v>814</v>
+      </c>
+      <c r="J64" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>816</v>
+      </c>
+      <c r="B65">
+        <v>400505</v>
+      </c>
+      <c r="C65" s="51">
+        <v>1</v>
+      </c>
+      <c r="D65" s="51"/>
+      <c r="E65" t="s">
+        <v>817</v>
+      </c>
+      <c r="H65" t="s">
+        <v>818</v>
+      </c>
+      <c r="I65" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>820</v>
+      </c>
+      <c r="B66">
+        <v>402704</v>
+      </c>
+      <c r="C66" s="51">
+        <v>1</v>
+      </c>
+      <c r="D66" s="51"/>
+      <c r="E66" t="s">
+        <v>821</v>
+      </c>
+      <c r="H66" t="s">
+        <v>822</v>
+      </c>
+      <c r="I66" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>824</v>
+      </c>
+      <c r="B67">
+        <v>402005</v>
+      </c>
+      <c r="C67" s="51">
+        <v>1</v>
+      </c>
+      <c r="D67" s="51"/>
+      <c r="E67" t="s">
+        <v>825</v>
+      </c>
+      <c r="H67" t="s">
+        <v>826</v>
+      </c>
+      <c r="I67" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>828</v>
+      </c>
+      <c r="B68">
+        <v>404603</v>
+      </c>
+      <c r="C68" s="51">
+        <v>1</v>
+      </c>
+      <c r="D68" s="51"/>
+      <c r="E68" t="s">
+        <v>829</v>
+      </c>
+      <c r="H68" t="s">
+        <v>830</v>
+      </c>
+      <c r="I68" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>832</v>
+      </c>
+      <c r="B69">
+        <v>400905</v>
+      </c>
+      <c r="C69" s="51">
+        <v>1</v>
+      </c>
+      <c r="D69" s="51"/>
+      <c r="E69" t="s">
+        <v>833</v>
+      </c>
+      <c r="H69" t="s">
+        <v>834</v>
+      </c>
+      <c r="I69" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>836</v>
+      </c>
+      <c r="B70">
+        <v>401305</v>
+      </c>
+      <c r="C70" s="51">
+        <v>1</v>
+      </c>
+      <c r="D70" s="51"/>
+      <c r="E70" t="s">
+        <v>837</v>
+      </c>
+      <c r="H70" t="s">
+        <v>838</v>
+      </c>
+      <c r="I70" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>840</v>
+      </c>
+      <c r="B71">
+        <v>401004</v>
+      </c>
+      <c r="C71" s="51">
+        <v>1</v>
+      </c>
+      <c r="D71" s="51"/>
+      <c r="E71" t="s">
+        <v>841</v>
+      </c>
+      <c r="H71" t="s">
+        <v>842</v>
+      </c>
+      <c r="I71" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>844</v>
+      </c>
+      <c r="B72">
+        <v>400406</v>
+      </c>
+      <c r="C72" s="51">
+        <v>1</v>
+      </c>
+      <c r="D72" s="51"/>
+      <c r="E72" t="s">
+        <v>845</v>
+      </c>
+      <c r="H72" t="s">
+        <v>846</v>
+      </c>
+      <c r="I72" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>848</v>
+      </c>
+      <c r="B73">
+        <v>404704</v>
+      </c>
+      <c r="C73" s="51">
+        <v>1</v>
+      </c>
+      <c r="D73" s="51"/>
+      <c r="E73" t="s">
+        <v>849</v>
+      </c>
+      <c r="H73" t="s">
+        <v>850</v>
+      </c>
+      <c r="I73" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>852</v>
+      </c>
+      <c r="B74">
+        <v>403004</v>
+      </c>
+      <c r="C74" s="51">
+        <v>1</v>
+      </c>
+      <c r="D74" s="51"/>
+      <c r="E74" t="s">
+        <v>853</v>
+      </c>
+      <c r="H74" t="s">
+        <v>854</v>
+      </c>
+      <c r="I74" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>856</v>
+      </c>
+      <c r="B75">
+        <v>406803</v>
+      </c>
+      <c r="C75" s="51">
+        <v>1</v>
+      </c>
+      <c r="D75" s="51"/>
+      <c r="E75" t="s">
+        <v>857</v>
+      </c>
+      <c r="H75" t="s">
+        <v>858</v>
+      </c>
+      <c r="I75" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>860</v>
+      </c>
+      <c r="B76">
+        <v>407602</v>
+      </c>
+      <c r="C76" s="51">
+        <v>1</v>
+      </c>
+      <c r="D76" s="51"/>
+      <c r="E76" t="s">
+        <v>861</v>
+      </c>
+      <c r="H76" t="s">
+        <v>862</v>
+      </c>
+      <c r="I76" t="s">
+        <v>863</v>
+      </c>
+      <c r="J76" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>865</v>
+      </c>
+      <c r="B77">
+        <v>406703</v>
+      </c>
+      <c r="C77" s="51">
+        <v>1</v>
+      </c>
+      <c r="D77" s="51"/>
+      <c r="E77" t="s">
+        <v>866</v>
+      </c>
+      <c r="H77" t="s">
+        <v>867</v>
+      </c>
+      <c r="I77" t="s">
+        <v>868</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="16" type="noConversion"/>
   <conditionalFormatting sqref="B52">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B53">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B53">
+  <conditionalFormatting sqref="B54:B55">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/source/bin/excel/character.xlsx
+++ b/source/bin/excel/character.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\liqi-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E63F8A68-F9F8-444D-8C87-D78B2A596040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85F5CA3D-F818-44B3-864D-1A23323237F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="export" sheetId="4" r:id="rId1"/>
@@ -19,7 +19,18 @@
     <sheet name="skin" sheetId="7" r:id="rId4"/>
     <sheet name="解锁类型描述" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -44496,7 +44507,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
         <v>726</v>
       </c>
@@ -44519,7 +44530,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
         <v>725</v>
       </c>
@@ -44542,7 +44553,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
         <v>749</v>
       </c>
@@ -44562,7 +44573,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
         <v>753</v>
       </c>
@@ -44585,7 +44596,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
         <v>754</v>
       </c>
@@ -44608,7 +44619,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
         <v>770</v>
       </c>
@@ -44629,7 +44640,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
         <v>774</v>
       </c>
@@ -44652,7 +44663,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>778</v>
       </c>
@@ -44672,8 +44683,11 @@
       <c r="I56" t="s">
         <v>781</v>
       </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>782</v>
       </c>
@@ -44693,8 +44707,11 @@
       <c r="I57" t="s">
         <v>785</v>
       </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>786</v>
       </c>
@@ -44717,8 +44734,11 @@
       <c r="J58" t="s">
         <v>790</v>
       </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>791</v>
       </c>
@@ -44738,8 +44758,11 @@
       <c r="I59" t="s">
         <v>794</v>
       </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>795</v>
       </c>
@@ -44759,8 +44782,11 @@
       <c r="I60" t="s">
         <v>798</v>
       </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>799</v>
       </c>
@@ -44780,8 +44806,11 @@
       <c r="I61" t="s">
         <v>802</v>
       </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>803</v>
       </c>
@@ -44801,8 +44830,11 @@
       <c r="I62" t="s">
         <v>806</v>
       </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>807</v>
       </c>
@@ -44822,8 +44854,11 @@
       <c r="I63" t="s">
         <v>810</v>
       </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>811</v>
       </c>
@@ -44846,8 +44881,11 @@
       <c r="J64" t="s">
         <v>815</v>
       </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>816</v>
       </c>
@@ -44867,8 +44905,11 @@
       <c r="I65" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>820</v>
       </c>
@@ -44888,8 +44929,11 @@
       <c r="I66" t="s">
         <v>823</v>
       </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>824</v>
       </c>
@@ -44909,8 +44953,11 @@
       <c r="I67" t="s">
         <v>827</v>
       </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>828</v>
       </c>
@@ -44930,8 +44977,11 @@
       <c r="I68" t="s">
         <v>831</v>
       </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>832</v>
       </c>
@@ -44951,8 +45001,11 @@
       <c r="I69" t="s">
         <v>835</v>
       </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>836</v>
       </c>
@@ -44972,8 +45025,11 @@
       <c r="I70" t="s">
         <v>839</v>
       </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>840</v>
       </c>
@@ -44993,8 +45049,11 @@
       <c r="I71" t="s">
         <v>843</v>
       </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>844</v>
       </c>
@@ -45014,8 +45073,11 @@
       <c r="I72" t="s">
         <v>847</v>
       </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>848</v>
       </c>
@@ -45035,8 +45097,11 @@
       <c r="I73" t="s">
         <v>851</v>
       </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>852</v>
       </c>
@@ -45056,8 +45121,11 @@
       <c r="I74" t="s">
         <v>855</v>
       </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>856</v>
       </c>
@@ -45077,8 +45145,11 @@
       <c r="I75" t="s">
         <v>859</v>
       </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>860</v>
       </c>
@@ -45101,8 +45172,11 @@
       <c r="J76" t="s">
         <v>864</v>
       </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>865</v>
       </c>
@@ -45121,6 +45195,9 @@
       </c>
       <c r="I77" t="s">
         <v>868</v>
+      </c>
+      <c r="K77">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
